--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="888" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="164">
   <si>
     <t>Materia</t>
   </si>
@@ -999,10 +999,10 @@
         <v>9</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E4">
         <v>10</v>
@@ -1053,10 +1053,10 @@
         <v>9</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W4">
         <v>10</v>
@@ -1076,10 +1076,10 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -1130,10 +1130,10 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -1153,10 +1153,10 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E6">
         <v>5</v>
@@ -1207,10 +1207,10 @@
         <v>7</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W6">
         <v>5</v>
@@ -1230,10 +1230,10 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E7">
         <v>10</v>
@@ -1284,10 +1284,10 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W7">
         <v>10</v>
@@ -1307,10 +1307,10 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E8">
         <v>10</v>
@@ -1361,10 +1361,10 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W8">
         <v>10</v>
@@ -1384,10 +1384,10 @@
         <v>7</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E9">
         <v>9</v>
@@ -1438,10 +1438,10 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1461,10 +1461,10 @@
         <v>6</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1515,10 +1515,10 @@
         <v>6</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1538,10 +1538,10 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E11">
         <v>10</v>
@@ -1592,10 +1592,10 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1615,10 +1615,10 @@
         <v>7</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E12">
         <v>7</v>
@@ -1669,10 +1669,10 @@
         <v>7</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>7</v>
@@ -1692,10 +1692,10 @@
         <v>6</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E13">
         <v>6</v>
@@ -1746,10 +1746,10 @@
         <v>6</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W13">
         <v>6</v>
@@ -1769,10 +1769,10 @@
         <v>10</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>8</v>
@@ -1823,10 +1823,10 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>8</v>
@@ -1846,10 +1846,10 @@
         <v>10</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E15">
         <v>9</v>
@@ -1900,10 +1900,10 @@
         <v>10</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1923,10 +1923,10 @@
         <v>7</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E16">
         <v>7</v>
@@ -1977,10 +1977,10 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W16">
         <v>7</v>
@@ -2000,10 +2000,10 @@
         <v>4</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E17">
         <v>9</v>
@@ -2054,10 +2054,10 @@
         <v>5</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2077,10 +2077,10 @@
         <v>7</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E18">
         <v>7</v>
@@ -2131,10 +2131,10 @@
         <v>7</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W18">
         <v>7</v>
@@ -2154,10 +2154,10 @@
         <v>9</v>
       </c>
       <c r="C19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E19">
         <v>9</v>
@@ -2208,10 +2208,10 @@
         <v>9</v>
       </c>
       <c r="U19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2231,10 +2231,10 @@
         <v>5</v>
       </c>
       <c r="C20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E20">
         <v>5</v>
@@ -2285,10 +2285,10 @@
         <v>5</v>
       </c>
       <c r="U20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W20">
         <v>5</v>
@@ -2308,10 +2308,10 @@
         <v>10</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E21">
         <v>8</v>
@@ -2362,10 +2362,10 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W21">
         <v>8</v>
@@ -2385,10 +2385,10 @@
         <v>9</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E22">
         <v>7</v>
@@ -2439,10 +2439,10 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>7</v>
@@ -2462,10 +2462,10 @@
         <v>10</v>
       </c>
       <c r="C23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="E23">
         <v>9</v>
@@ -2516,10 +2516,10 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="W23">
         <v>9</v>
@@ -2539,10 +2539,10 @@
         <v>8</v>
       </c>
       <c r="C24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E24">
         <v>5</v>
@@ -2593,10 +2593,10 @@
         <v>8</v>
       </c>
       <c r="U24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2616,10 +2616,10 @@
         <v>8</v>
       </c>
       <c r="C25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E25">
         <v>7</v>
@@ -2670,10 +2670,10 @@
         <v>8</v>
       </c>
       <c r="U25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W25">
         <v>7</v>
@@ -2693,10 +2693,10 @@
         <v>4</v>
       </c>
       <c r="C26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E26">
         <v>5</v>
@@ -2747,10 +2747,10 @@
         <v>5</v>
       </c>
       <c r="U26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2770,10 +2770,10 @@
         <v>9</v>
       </c>
       <c r="C27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E27">
         <v>9</v>
@@ -2824,10 +2824,10 @@
         <v>9</v>
       </c>
       <c r="U27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W27">
         <v>9</v>
@@ -2847,10 +2847,10 @@
         <v>6</v>
       </c>
       <c r="C28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E28">
         <v>6</v>
@@ -2901,10 +2901,10 @@
         <v>6</v>
       </c>
       <c r="U28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W28">
         <v>6</v>
@@ -2924,10 +2924,10 @@
         <v>4</v>
       </c>
       <c r="C29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E29">
         <v>9</v>
@@ -2978,10 +2978,10 @@
         <v>5</v>
       </c>
       <c r="U29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W29">
         <v>9</v>
@@ -3001,10 +3001,10 @@
         <v>9</v>
       </c>
       <c r="C30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E30">
         <v>6</v>
@@ -3055,10 +3055,10 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>6</v>
@@ -3078,10 +3078,10 @@
         <v>8</v>
       </c>
       <c r="C31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E31">
         <v>7</v>
@@ -3132,10 +3132,10 @@
         <v>8</v>
       </c>
       <c r="U31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W31">
         <v>7</v>
@@ -3155,10 +3155,10 @@
         <v>9</v>
       </c>
       <c r="C32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E32">
         <v>9</v>
@@ -3209,10 +3209,10 @@
         <v>9</v>
       </c>
       <c r="U32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>9</v>
@@ -3232,10 +3232,10 @@
         <v>7</v>
       </c>
       <c r="C33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E33">
         <v>8</v>
@@ -3286,10 +3286,10 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3309,10 +3309,10 @@
         <v>8</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="E34">
         <v>7</v>
@@ -3363,10 +3363,10 @@
         <v>8</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="W34">
         <v>7</v>
@@ -3386,10 +3386,10 @@
         <v>5</v>
       </c>
       <c r="C35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E35">
         <v>7</v>
@@ -3440,10 +3440,10 @@
         <v>5</v>
       </c>
       <c r="U35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V35">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W35">
         <v>7</v>
@@ -3463,10 +3463,10 @@
         <v>10</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E36">
         <v>5</v>
@@ -3517,10 +3517,10 @@
         <v>10</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3540,10 +3540,10 @@
         <v>10</v>
       </c>
       <c r="C37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="E37">
         <v>7</v>
@@ -3594,10 +3594,10 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="W37">
         <v>7</v>
@@ -3617,10 +3617,10 @@
         <v>10</v>
       </c>
       <c r="C38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E38">
         <v>9</v>
@@ -3671,10 +3671,10 @@
         <v>10</v>
       </c>
       <c r="U38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W38">
         <v>9</v>
@@ -3694,10 +3694,10 @@
         <v>8</v>
       </c>
       <c r="C39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E39">
         <v>9</v>
@@ -3748,10 +3748,10 @@
         <v>8</v>
       </c>
       <c r="U39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="W39">
         <v>9</v>
@@ -3771,10 +3771,10 @@
         <v>8</v>
       </c>
       <c r="C40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="E40">
         <v>9</v>
@@ -3825,10 +3825,10 @@
         <v>8</v>
       </c>
       <c r="U40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3958,10 +3958,10 @@
         <v>100</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E4">
         <v>100</v>
@@ -4017,10 +4017,10 @@
         <v>100</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E5">
         <v>100</v>
@@ -4076,10 +4076,10 @@
         <v>96.7</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E6">
         <v>80</v>
@@ -4135,10 +4135,10 @@
         <v>100</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E7">
         <v>100</v>
@@ -4194,10 +4194,10 @@
         <v>100</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E8">
         <v>100</v>
@@ -4253,10 +4253,10 @@
         <v>100</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E9">
         <v>85</v>
@@ -4312,10 +4312,10 @@
         <v>96.7</v>
       </c>
       <c r="C10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>75</v>
@@ -4371,10 +4371,10 @@
         <v>100</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E11">
         <v>100</v>
@@ -4430,10 +4430,10 @@
         <v>93.3</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E12">
         <v>85</v>
@@ -4489,10 +4489,10 @@
         <v>96.7</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E13">
         <v>85</v>
@@ -4548,10 +4548,10 @@
         <v>100</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>100</v>
@@ -4607,10 +4607,10 @@
         <v>96.7</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E15">
         <v>100</v>
@@ -4666,10 +4666,10 @@
         <v>100</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E16">
         <v>85</v>
@@ -4725,10 +4725,10 @@
         <v>93.3</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E17">
         <v>90</v>
@@ -4784,10 +4784,10 @@
         <v>93.3</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E18">
         <v>100</v>
@@ -4843,10 +4843,10 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>90</v>
@@ -4902,10 +4902,10 @@
         <v>83.3</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E20">
         <v>55</v>
@@ -4961,10 +4961,10 @@
         <v>100</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E21">
         <v>95</v>
@@ -5020,10 +5020,10 @@
         <v>96.7</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E22">
         <v>95</v>
@@ -5079,10 +5079,10 @@
         <v>100</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E23">
         <v>100</v>
@@ -5138,10 +5138,10 @@
         <v>93.3</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E24">
         <v>80</v>
@@ -5197,10 +5197,10 @@
         <v>93.3</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E25">
         <v>90</v>
@@ -5256,10 +5256,10 @@
         <v>90</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>75</v>
@@ -5315,10 +5315,10 @@
         <v>100</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E27">
         <v>100</v>
@@ -5374,10 +5374,10 @@
         <v>93.3</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E28">
         <v>90</v>
@@ -5433,10 +5433,10 @@
         <v>93.3</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29">
         <v>95</v>
@@ -5492,10 +5492,10 @@
         <v>93.3</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E30">
         <v>95</v>
@@ -5551,10 +5551,10 @@
         <v>100</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E31">
         <v>95</v>
@@ -5610,10 +5610,10 @@
         <v>100</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E32">
         <v>85</v>
@@ -5669,10 +5669,10 @@
         <v>96.7</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="D33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E33">
         <v>85</v>
@@ -5728,10 +5728,10 @@
         <v>93.3</v>
       </c>
       <c r="C34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E34">
         <v>85</v>
@@ -5787,10 +5787,10 @@
         <v>93.3</v>
       </c>
       <c r="C35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E35">
         <v>100</v>
@@ -5846,10 +5846,10 @@
         <v>100</v>
       </c>
       <c r="C36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E36">
         <v>90</v>
@@ -5905,10 +5905,10 @@
         <v>100</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E37">
         <v>95</v>
@@ -5964,10 +5964,10 @@
         <v>100</v>
       </c>
       <c r="C38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E38">
         <v>85</v>
@@ -6023,10 +6023,10 @@
         <v>93.3</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E39">
         <v>85</v>
@@ -6082,10 +6082,10 @@
         <v>100</v>
       </c>
       <c r="C40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="D40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E40">
         <v>95</v>
@@ -6185,7 +6185,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>61</v>
@@ -6194,77 +6194,83 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>62.16</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>37.84</v>
+      </c>
+      <c r="H2">
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>37</v>
       </c>
       <c r="D3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>83.78</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>16.22</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
       </c>
       <c r="I3">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="J3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C4">
         <v>37</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>83.78</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="G4">
-        <v>16.22</v>
+        <v>13.51</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6275,10 +6281,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>37</v>
@@ -6296,7 +6302,7 @@
         <v>13.51</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6307,28 +6313,28 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C6">
         <v>37</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>86.48999999999999</v>
+        <v>89.19</v>
       </c>
       <c r="G6">
-        <v>13.51</v>
+        <v>10.81</v>
       </c>
       <c r="H6">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6339,7 +6345,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>61</v>
@@ -6348,16 +6354,16 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>89.19</v>
+        <v>91.89</v>
       </c>
       <c r="G7">
-        <v>10.81</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -6376,7 +6382,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6401,1486 +6407,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920029</v>
-      </c>
-      <c r="B2" t="s">
-        <v>68</v>
-      </c>
-      <c r="C2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" t="s">
-        <v>127</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920029</v>
-      </c>
-      <c r="B3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C3" t="s">
-        <v>89</v>
-      </c>
-      <c r="D3" t="s">
-        <v>127</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920030</v>
-      </c>
-      <c r="B4" t="s">
-        <v>69</v>
-      </c>
-      <c r="C4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D4" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920030</v>
-      </c>
-      <c r="B5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920031</v>
-      </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>101</v>
-      </c>
-      <c r="D6" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920031</v>
-      </c>
-      <c r="B7" t="s">
-        <v>70</v>
-      </c>
-      <c r="C7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D7" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920032</v>
-      </c>
-      <c r="B8" t="s">
-        <v>71</v>
-      </c>
-      <c r="C8" t="s">
-        <v>89</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920032</v>
-      </c>
-      <c r="B9" t="s">
-        <v>71</v>
-      </c>
-      <c r="C9" t="s">
-        <v>89</v>
-      </c>
-      <c r="D9" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920033</v>
-      </c>
-      <c r="B10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" t="s">
-        <v>102</v>
-      </c>
-      <c r="D10" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920033</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" t="s">
-        <v>131</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920323</v>
-      </c>
-      <c r="B12" t="s">
-        <v>73</v>
-      </c>
-      <c r="C12" t="s">
-        <v>79</v>
-      </c>
-      <c r="D12" t="s">
-        <v>132</v>
-      </c>
-      <c r="E12" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920323</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D13" t="s">
-        <v>132</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920034</v>
-      </c>
-      <c r="B14" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" t="s">
-        <v>91</v>
-      </c>
-      <c r="D14" t="s">
-        <v>133</v>
-      </c>
-      <c r="E14" t="s">
-        <v>7</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920034</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>91</v>
-      </c>
-      <c r="D15" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920182</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E16" t="s">
-        <v>7</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920182</v>
-      </c>
-      <c r="B17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17" t="s">
-        <v>134</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920035</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>103</v>
-      </c>
-      <c r="D18" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" t="s">
-        <v>7</v>
-      </c>
-      <c r="F18" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920035</v>
-      </c>
-      <c r="B19" t="s">
-        <v>76</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920036</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>104</v>
-      </c>
-      <c r="D20" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" t="s">
-        <v>7</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920036</v>
-      </c>
-      <c r="B21" t="s">
-        <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>104</v>
-      </c>
-      <c r="D21" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920037</v>
-      </c>
-      <c r="B22" t="s">
-        <v>78</v>
-      </c>
-      <c r="C22" t="s">
-        <v>101</v>
-      </c>
-      <c r="D22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" t="s">
-        <v>7</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920037</v>
-      </c>
-      <c r="B23" t="s">
-        <v>78</v>
-      </c>
-      <c r="C23" t="s">
-        <v>101</v>
-      </c>
-      <c r="D23" t="s">
-        <v>137</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>22330051920038</v>
-      </c>
-      <c r="B24" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>138</v>
-      </c>
-      <c r="E24" t="s">
-        <v>7</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920038</v>
-      </c>
-      <c r="B25" t="s">
-        <v>79</v>
-      </c>
-      <c r="C25" t="s">
-        <v>105</v>
-      </c>
-      <c r="D25" t="s">
-        <v>138</v>
-      </c>
-      <c r="E25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920331</v>
-      </c>
-      <c r="B26" t="s">
-        <v>80</v>
-      </c>
-      <c r="C26" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" t="s">
-        <v>139</v>
-      </c>
-      <c r="E26" t="s">
-        <v>7</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920331</v>
-      </c>
-      <c r="B27" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" t="s">
-        <v>84</v>
-      </c>
-      <c r="D27" t="s">
-        <v>139</v>
-      </c>
-      <c r="E27" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920189</v>
-      </c>
-      <c r="B28" t="s">
-        <v>81</v>
-      </c>
-      <c r="C28" t="s">
-        <v>106</v>
-      </c>
-      <c r="D28" t="s">
-        <v>140</v>
-      </c>
-      <c r="E28" t="s">
-        <v>7</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920189</v>
-      </c>
-      <c r="B29" t="s">
-        <v>81</v>
-      </c>
-      <c r="C29" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E29" t="s">
-        <v>6</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920039</v>
-      </c>
-      <c r="B30" t="s">
-        <v>82</v>
-      </c>
-      <c r="C30" t="s">
-        <v>107</v>
-      </c>
-      <c r="D30" t="s">
-        <v>141</v>
-      </c>
-      <c r="E30" t="s">
-        <v>7</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920039</v>
-      </c>
-      <c r="B31" t="s">
-        <v>82</v>
-      </c>
-      <c r="C31" t="s">
-        <v>107</v>
-      </c>
-      <c r="D31" t="s">
-        <v>141</v>
-      </c>
-      <c r="E31" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32">
-        <v>22330051920191</v>
-      </c>
-      <c r="B32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C32" t="s">
-        <v>108</v>
-      </c>
-      <c r="D32" t="s">
-        <v>142</v>
-      </c>
-      <c r="E32" t="s">
-        <v>7</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33">
-        <v>22330051920191</v>
-      </c>
-      <c r="B33" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" t="s">
-        <v>108</v>
-      </c>
-      <c r="D33" t="s">
-        <v>142</v>
-      </c>
-      <c r="E33" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
-      <c r="A34">
-        <v>22330051920325</v>
-      </c>
-      <c r="B34" t="s">
-        <v>84</v>
-      </c>
-      <c r="C34" t="s">
-        <v>102</v>
-      </c>
-      <c r="D34" t="s">
-        <v>143</v>
-      </c>
-      <c r="E34" t="s">
-        <v>7</v>
-      </c>
-      <c r="F34" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35">
-        <v>22330051920325</v>
-      </c>
-      <c r="B35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D35" t="s">
-        <v>143</v>
-      </c>
-      <c r="E35" t="s">
-        <v>6</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36">
-        <v>22330051920040</v>
-      </c>
-      <c r="B36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" t="s">
-        <v>109</v>
-      </c>
-      <c r="D36" t="s">
-        <v>144</v>
-      </c>
-      <c r="E36" t="s">
-        <v>7</v>
-      </c>
-      <c r="F36" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
-      <c r="A37">
-        <v>22330051920040</v>
-      </c>
-      <c r="B37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C37" t="s">
-        <v>109</v>
-      </c>
-      <c r="D37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E37" t="s">
-        <v>6</v>
-      </c>
-      <c r="F37" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38">
-        <v>22330051920041</v>
-      </c>
-      <c r="B38" t="s">
-        <v>86</v>
-      </c>
-      <c r="C38" t="s">
-        <v>110</v>
-      </c>
-      <c r="D38" t="s">
-        <v>145</v>
-      </c>
-      <c r="E38" t="s">
-        <v>7</v>
-      </c>
-      <c r="F38" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39">
-        <v>22330051920041</v>
-      </c>
-      <c r="B39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C39" t="s">
-        <v>110</v>
-      </c>
-      <c r="D39" t="s">
-        <v>145</v>
-      </c>
-      <c r="E39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F39" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40">
-        <v>22330051920043</v>
-      </c>
-      <c r="B40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40" t="s">
-        <v>146</v>
-      </c>
-      <c r="E40" t="s">
-        <v>7</v>
-      </c>
-      <c r="F40" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41">
-        <v>22330051920043</v>
-      </c>
-      <c r="B41" t="s">
-        <v>87</v>
-      </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41" t="s">
-        <v>146</v>
-      </c>
-      <c r="E41" t="s">
-        <v>6</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42">
-        <v>22330051920042</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>111</v>
-      </c>
-      <c r="D42" t="s">
-        <v>147</v>
-      </c>
-      <c r="E42" t="s">
-        <v>7</v>
-      </c>
-      <c r="F42" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43">
-        <v>22330051920042</v>
-      </c>
-      <c r="B43" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" t="s">
-        <v>147</v>
-      </c>
-      <c r="E43" t="s">
-        <v>6</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44">
-        <v>22330051920327</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>112</v>
-      </c>
-      <c r="D44" t="s">
-        <v>148</v>
-      </c>
-      <c r="E44" t="s">
-        <v>7</v>
-      </c>
-      <c r="F44" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45">
-        <v>22330051920327</v>
-      </c>
-      <c r="B45" t="s">
-        <v>89</v>
-      </c>
-      <c r="C45" t="s">
-        <v>112</v>
-      </c>
-      <c r="D45" t="s">
-        <v>148</v>
-      </c>
-      <c r="E45" t="s">
-        <v>6</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
-      <c r="A46">
-        <v>22330051920196</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>113</v>
-      </c>
-      <c r="D46" t="s">
-        <v>149</v>
-      </c>
-      <c r="E46" t="s">
-        <v>7</v>
-      </c>
-      <c r="F46" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
-      <c r="A47">
-        <v>22330051920196</v>
-      </c>
-      <c r="B47" t="s">
-        <v>90</v>
-      </c>
-      <c r="C47" t="s">
-        <v>113</v>
-      </c>
-      <c r="D47" t="s">
-        <v>149</v>
-      </c>
-      <c r="E47" t="s">
-        <v>6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
-      <c r="A48">
-        <v>22330051920044</v>
-      </c>
-      <c r="B48" t="s">
-        <v>90</v>
-      </c>
-      <c r="C48" t="s">
-        <v>114</v>
-      </c>
-      <c r="D48" t="s">
-        <v>150</v>
-      </c>
-      <c r="E48" t="s">
-        <v>7</v>
-      </c>
-      <c r="F48" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
-      <c r="A49">
-        <v>22330051920044</v>
-      </c>
-      <c r="B49" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" t="s">
-        <v>114</v>
-      </c>
-      <c r="D49" t="s">
-        <v>150</v>
-      </c>
-      <c r="E49" t="s">
-        <v>6</v>
-      </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
-      <c r="A50">
-        <v>22330051920045</v>
-      </c>
-      <c r="B50" t="s">
-        <v>89</v>
-      </c>
-      <c r="C50" t="s">
-        <v>115</v>
-      </c>
-      <c r="D50" t="s">
-        <v>151</v>
-      </c>
-      <c r="E50" t="s">
-        <v>7</v>
-      </c>
-      <c r="F50" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
-      <c r="A51">
-        <v>22330051920045</v>
-      </c>
-      <c r="B51" t="s">
-        <v>89</v>
-      </c>
-      <c r="C51" t="s">
-        <v>115</v>
-      </c>
-      <c r="D51" t="s">
-        <v>151</v>
-      </c>
-      <c r="E51" t="s">
-        <v>6</v>
-      </c>
-      <c r="F51" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6">
-      <c r="A52">
-        <v>22330051920046</v>
-      </c>
-      <c r="B52" t="s">
-        <v>91</v>
-      </c>
-      <c r="C52" t="s">
-        <v>116</v>
-      </c>
-      <c r="D52" t="s">
-        <v>152</v>
-      </c>
-      <c r="E52" t="s">
-        <v>7</v>
-      </c>
-      <c r="F52" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6">
-      <c r="A53">
-        <v>22330051920046</v>
-      </c>
-      <c r="B53" t="s">
-        <v>91</v>
-      </c>
-      <c r="C53" t="s">
-        <v>116</v>
-      </c>
-      <c r="D53" t="s">
-        <v>152</v>
-      </c>
-      <c r="E53" t="s">
-        <v>6</v>
-      </c>
-      <c r="F53" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6">
-      <c r="A54">
-        <v>22330051920141</v>
-      </c>
-      <c r="B54" t="s">
-        <v>91</v>
-      </c>
-      <c r="C54" t="s">
-        <v>117</v>
-      </c>
-      <c r="D54" t="s">
-        <v>153</v>
-      </c>
-      <c r="E54" t="s">
-        <v>7</v>
-      </c>
-      <c r="F54" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6">
-      <c r="A55">
-        <v>22330051920141</v>
-      </c>
-      <c r="B55" t="s">
-        <v>91</v>
-      </c>
-      <c r="C55" t="s">
-        <v>117</v>
-      </c>
-      <c r="D55" t="s">
-        <v>153</v>
-      </c>
-      <c r="E55" t="s">
-        <v>6</v>
-      </c>
-      <c r="F55" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6">
-      <c r="A56">
-        <v>22330051920328</v>
-      </c>
-      <c r="B56" t="s">
-        <v>92</v>
-      </c>
-      <c r="C56" t="s">
-        <v>118</v>
-      </c>
-      <c r="D56" t="s">
-        <v>154</v>
-      </c>
-      <c r="E56" t="s">
-        <v>7</v>
-      </c>
-      <c r="F56" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6">
-      <c r="A57">
-        <v>22330051920328</v>
-      </c>
-      <c r="B57" t="s">
-        <v>92</v>
-      </c>
-      <c r="C57" t="s">
-        <v>118</v>
-      </c>
-      <c r="D57" t="s">
-        <v>154</v>
-      </c>
-      <c r="E57" t="s">
-        <v>6</v>
-      </c>
-      <c r="F57" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6">
-      <c r="A58">
-        <v>22330051920047</v>
-      </c>
-      <c r="B58" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" t="s">
-        <v>116</v>
-      </c>
-      <c r="D58" t="s">
-        <v>155</v>
-      </c>
-      <c r="E58" t="s">
-        <v>7</v>
-      </c>
-      <c r="F58" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6">
-      <c r="A59">
-        <v>22330051920047</v>
-      </c>
-      <c r="B59" t="s">
-        <v>93</v>
-      </c>
-      <c r="C59" t="s">
-        <v>116</v>
-      </c>
-      <c r="D59" t="s">
-        <v>155</v>
-      </c>
-      <c r="E59" t="s">
-        <v>6</v>
-      </c>
-      <c r="F59" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6">
-      <c r="A60">
-        <v>22330051920198</v>
-      </c>
-      <c r="B60" t="s">
-        <v>94</v>
-      </c>
-      <c r="C60" t="s">
-        <v>119</v>
-      </c>
-      <c r="D60" t="s">
-        <v>156</v>
-      </c>
-      <c r="E60" t="s">
-        <v>7</v>
-      </c>
-      <c r="F60" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6">
-      <c r="A61">
-        <v>22330051920198</v>
-      </c>
-      <c r="B61" t="s">
-        <v>94</v>
-      </c>
-      <c r="C61" t="s">
-        <v>119</v>
-      </c>
-      <c r="D61" t="s">
-        <v>156</v>
-      </c>
-      <c r="E61" t="s">
-        <v>6</v>
-      </c>
-      <c r="F61" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6">
-      <c r="A62">
-        <v>22330051920048</v>
-      </c>
-      <c r="B62" t="s">
-        <v>95</v>
-      </c>
-      <c r="C62" t="s">
-        <v>120</v>
-      </c>
-      <c r="D62" t="s">
-        <v>157</v>
-      </c>
-      <c r="E62" t="s">
-        <v>7</v>
-      </c>
-      <c r="F62" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6">
-      <c r="A63">
-        <v>22330051920048</v>
-      </c>
-      <c r="B63" t="s">
-        <v>95</v>
-      </c>
-      <c r="C63" t="s">
-        <v>120</v>
-      </c>
-      <c r="D63" t="s">
-        <v>157</v>
-      </c>
-      <c r="E63" t="s">
-        <v>6</v>
-      </c>
-      <c r="F63" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6">
-      <c r="A64">
-        <v>22330051920336</v>
-      </c>
-      <c r="B64" t="s">
-        <v>96</v>
-      </c>
-      <c r="C64" t="s">
-        <v>121</v>
-      </c>
-      <c r="D64" t="s">
-        <v>158</v>
-      </c>
-      <c r="E64" t="s">
-        <v>7</v>
-      </c>
-      <c r="F64" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6">
-      <c r="A65">
-        <v>22330051920336</v>
-      </c>
-      <c r="B65" t="s">
-        <v>96</v>
-      </c>
-      <c r="C65" t="s">
-        <v>121</v>
-      </c>
-      <c r="D65" t="s">
-        <v>158</v>
-      </c>
-      <c r="E65" t="s">
-        <v>6</v>
-      </c>
-      <c r="F65" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6">
-      <c r="A66">
-        <v>22330051920049</v>
-      </c>
-      <c r="B66" t="s">
-        <v>96</v>
-      </c>
-      <c r="C66" t="s">
-        <v>122</v>
-      </c>
-      <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" t="s">
-        <v>7</v>
-      </c>
-      <c r="F66" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6">
-      <c r="A67">
-        <v>22330051920049</v>
-      </c>
-      <c r="B67" t="s">
-        <v>96</v>
-      </c>
-      <c r="C67" t="s">
-        <v>122</v>
-      </c>
-      <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" t="s">
-        <v>6</v>
-      </c>
-      <c r="F67" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6">
-      <c r="A68">
-        <v>22330051920329</v>
-      </c>
-      <c r="B68" t="s">
-        <v>97</v>
-      </c>
-      <c r="C68" t="s">
-        <v>123</v>
-      </c>
-      <c r="D68" t="s">
-        <v>160</v>
-      </c>
-      <c r="E68" t="s">
-        <v>7</v>
-      </c>
-      <c r="F68" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6">
-      <c r="A69">
-        <v>22330051920329</v>
-      </c>
-      <c r="B69" t="s">
-        <v>97</v>
-      </c>
-      <c r="C69" t="s">
-        <v>123</v>
-      </c>
-      <c r="D69" t="s">
-        <v>160</v>
-      </c>
-      <c r="E69" t="s">
-        <v>6</v>
-      </c>
-      <c r="F69" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6">
-      <c r="A70">
-        <v>22330051920203</v>
-      </c>
-      <c r="B70" t="s">
-        <v>98</v>
-      </c>
-      <c r="C70" t="s">
-        <v>124</v>
-      </c>
-      <c r="D70" t="s">
-        <v>161</v>
-      </c>
-      <c r="E70" t="s">
-        <v>7</v>
-      </c>
-      <c r="F70" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6">
-      <c r="A71">
-        <v>22330051920203</v>
-      </c>
-      <c r="B71" t="s">
-        <v>98</v>
-      </c>
-      <c r="C71" t="s">
-        <v>124</v>
-      </c>
-      <c r="D71" t="s">
-        <v>161</v>
-      </c>
-      <c r="E71" t="s">
-        <v>6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6">
-      <c r="A72">
-        <v>22330051920050</v>
-      </c>
-      <c r="B72" t="s">
-        <v>99</v>
-      </c>
-      <c r="C72" t="s">
-        <v>125</v>
-      </c>
-      <c r="D72" t="s">
-        <v>162</v>
-      </c>
-      <c r="E72" t="s">
-        <v>7</v>
-      </c>
-      <c r="F72" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6">
-      <c r="A73">
-        <v>22330051920050</v>
-      </c>
-      <c r="B73" t="s">
-        <v>99</v>
-      </c>
-      <c r="C73" t="s">
-        <v>125</v>
-      </c>
-      <c r="D73" t="s">
-        <v>162</v>
-      </c>
-      <c r="E73" t="s">
-        <v>6</v>
-      </c>
-      <c r="F73" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6">
-      <c r="A74">
-        <v>22330051920051</v>
-      </c>
-      <c r="B74" t="s">
-        <v>99</v>
-      </c>
-      <c r="C74" t="s">
-        <v>126</v>
-      </c>
-      <c r="D74" t="s">
-        <v>163</v>
-      </c>
-      <c r="E74" t="s">
-        <v>7</v>
-      </c>
-      <c r="F74" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6">
-      <c r="A75">
-        <v>22330051920051</v>
-      </c>
-      <c r="B75" t="s">
-        <v>99</v>
-      </c>
-      <c r="C75" t="s">
-        <v>126</v>
-      </c>
-      <c r="D75" t="s">
-        <v>163</v>
-      </c>
-      <c r="E75" t="s">
-        <v>6</v>
-      </c>
-      <c r="F75" t="s">
-        <v>61</v>
       </c>
     </row>
   </sheetData>
@@ -7928,7 +6454,7 @@
         <v>127</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -7945,7 +6471,7 @@
         <v>128</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7962,7 +6488,7 @@
         <v>129</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -7979,7 +6505,7 @@
         <v>130</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -7996,7 +6522,7 @@
         <v>131</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -8013,7 +6539,7 @@
         <v>132</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -8030,7 +6556,7 @@
         <v>133</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -8047,7 +6573,7 @@
         <v>134</v>
       </c>
       <c r="E9">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -8064,7 +6590,7 @@
         <v>135</v>
       </c>
       <c r="E10">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -8081,7 +6607,7 @@
         <v>136</v>
       </c>
       <c r="E11">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -8098,7 +6624,7 @@
         <v>137</v>
       </c>
       <c r="E12">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -8115,7 +6641,7 @@
         <v>138</v>
       </c>
       <c r="E13">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -8132,7 +6658,7 @@
         <v>139</v>
       </c>
       <c r="E14">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -8149,7 +6675,7 @@
         <v>140</v>
       </c>
       <c r="E15">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -8166,7 +6692,7 @@
         <v>141</v>
       </c>
       <c r="E16">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -8183,7 +6709,7 @@
         <v>142</v>
       </c>
       <c r="E17">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -8200,7 +6726,7 @@
         <v>143</v>
       </c>
       <c r="E18">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -8217,7 +6743,7 @@
         <v>144</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -8234,7 +6760,7 @@
         <v>145</v>
       </c>
       <c r="E20">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -8251,7 +6777,7 @@
         <v>146</v>
       </c>
       <c r="E21">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -8268,7 +6794,7 @@
         <v>147</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -8285,7 +6811,7 @@
         <v>148</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -8302,7 +6828,7 @@
         <v>149</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -8319,7 +6845,7 @@
         <v>150</v>
       </c>
       <c r="E25">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -8336,7 +6862,7 @@
         <v>151</v>
       </c>
       <c r="E26">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -8353,7 +6879,7 @@
         <v>152</v>
       </c>
       <c r="E27">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -8370,7 +6896,7 @@
         <v>153</v>
       </c>
       <c r="E28">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -8387,7 +6913,7 @@
         <v>154</v>
       </c>
       <c r="E29">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -8404,7 +6930,7 @@
         <v>155</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -8421,7 +6947,7 @@
         <v>156</v>
       </c>
       <c r="E31">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -8438,7 +6964,7 @@
         <v>157</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -8455,7 +6981,7 @@
         <v>158</v>
       </c>
       <c r="E33">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -8472,7 +6998,7 @@
         <v>159</v>
       </c>
       <c r="E34">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -8489,7 +7015,7 @@
         <v>160</v>
       </c>
       <c r="E35">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -8506,7 +7032,7 @@
         <v>161</v>
       </c>
       <c r="E36">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -8523,7 +7049,7 @@
         <v>162</v>
       </c>
       <c r="E37">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -8540,7 +7066,7 @@
         <v>163</v>
       </c>
       <c r="E38">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8550,7 +7076,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G49"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -8582,16 +7108,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920029</v>
+        <v>22330051920031</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -8600,44 +7126,44 @@
         <v>61</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920029</v>
+        <v>22330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="D3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920030</v>
+        <v>22330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -8646,90 +7172,90 @@
         <v>61</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920030</v>
+        <v>22330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="D5" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="E5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920032</v>
+        <v>22330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D6" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
         <v>61</v>
       </c>
       <c r="G6">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920032</v>
+        <v>22330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="C7" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="D7" t="s">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
         <v>61</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920033</v>
+        <v>22330051920043</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -8738,90 +7264,90 @@
         <v>61</v>
       </c>
       <c r="G8">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920033</v>
+        <v>22330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920323</v>
+        <v>22330051920049</v>
       </c>
       <c r="B10" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C10" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="D10" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="E10" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F10" t="s">
         <v>61</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920323</v>
+        <v>22330051920049</v>
       </c>
       <c r="B11" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
       <c r="C11" t="s">
-        <v>79</v>
+        <v>122</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>159</v>
       </c>
       <c r="E11" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G11">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920182</v>
+        <v>22330051920050</v>
       </c>
       <c r="B12" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C12" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -8830,21 +7356,21 @@
         <v>61</v>
       </c>
       <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920182</v>
+        <v>22330051920050</v>
       </c>
       <c r="B13" t="s">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="C13" t="s">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="D13" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -8853,7 +7379,7 @@
         <v>61</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -8876,44 +7402,44 @@
         <v>61</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920035</v>
+        <v>22330051920036</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C15" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D15" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E15" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G15">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920037</v>
+        <v>22330051920141</v>
       </c>
       <c r="B16" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="C16" t="s">
-        <v>101</v>
+        <v>117</v>
       </c>
       <c r="D16" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -8922,766 +7448,53 @@
         <v>61</v>
       </c>
       <c r="G16">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920037</v>
+        <v>22330051920047</v>
       </c>
       <c r="B17" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>101</v>
+        <v>116</v>
       </c>
       <c r="D17" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="E17" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F17" t="s">
         <v>61</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920038</v>
+        <v>22330051920336</v>
       </c>
       <c r="B18" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C18" t="s">
-        <v>105</v>
+        <v>121</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>158</v>
       </c>
       <c r="E18" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F18" t="s">
         <v>61</v>
       </c>
       <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920038</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" t="s">
-        <v>138</v>
-      </c>
-      <c r="E19" t="s">
-        <v>7</v>
-      </c>
-      <c r="F19" t="s">
-        <v>61</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920331</v>
-      </c>
-      <c r="B20" t="s">
-        <v>80</v>
-      </c>
-      <c r="C20" t="s">
-        <v>84</v>
-      </c>
-      <c r="D20" t="s">
-        <v>139</v>
-      </c>
-      <c r="E20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F20" t="s">
-        <v>61</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920331</v>
-      </c>
-      <c r="B21" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" t="s">
-        <v>84</v>
-      </c>
-      <c r="D21" t="s">
-        <v>139</v>
-      </c>
-      <c r="E21" t="s">
-        <v>7</v>
-      </c>
-      <c r="F21" t="s">
-        <v>61</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920191</v>
-      </c>
-      <c r="B22" t="s">
-        <v>83</v>
-      </c>
-      <c r="C22" t="s">
-        <v>108</v>
-      </c>
-      <c r="D22" t="s">
-        <v>142</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>61</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920191</v>
-      </c>
-      <c r="B23" t="s">
-        <v>83</v>
-      </c>
-      <c r="C23" t="s">
-        <v>108</v>
-      </c>
-      <c r="D23" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F23" t="s">
-        <v>61</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920040</v>
-      </c>
-      <c r="B24" t="s">
-        <v>85</v>
-      </c>
-      <c r="C24" t="s">
-        <v>109</v>
-      </c>
-      <c r="D24" t="s">
-        <v>144</v>
-      </c>
-      <c r="E24" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" t="s">
-        <v>61</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920040</v>
-      </c>
-      <c r="B25" t="s">
-        <v>85</v>
-      </c>
-      <c r="C25" t="s">
-        <v>109</v>
-      </c>
-      <c r="D25" t="s">
-        <v>144</v>
-      </c>
-      <c r="E25" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" t="s">
-        <v>61</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920041</v>
-      </c>
-      <c r="B26" t="s">
-        <v>86</v>
-      </c>
-      <c r="C26" t="s">
-        <v>110</v>
-      </c>
-      <c r="D26" t="s">
-        <v>145</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>61</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920041</v>
-      </c>
-      <c r="B27" t="s">
-        <v>86</v>
-      </c>
-      <c r="C27" t="s">
-        <v>110</v>
-      </c>
-      <c r="D27" t="s">
-        <v>145</v>
-      </c>
-      <c r="E27" t="s">
-        <v>7</v>
-      </c>
-      <c r="F27" t="s">
-        <v>61</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920042</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>111</v>
-      </c>
-      <c r="D28" t="s">
-        <v>147</v>
-      </c>
-      <c r="E28" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" t="s">
-        <v>61</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920042</v>
-      </c>
-      <c r="B29" t="s">
-        <v>88</v>
-      </c>
-      <c r="C29" t="s">
-        <v>111</v>
-      </c>
-      <c r="D29" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>7</v>
-      </c>
-      <c r="F29" t="s">
-        <v>61</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920327</v>
-      </c>
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>112</v>
-      </c>
-      <c r="D30" t="s">
-        <v>148</v>
-      </c>
-      <c r="E30" t="s">
-        <v>6</v>
-      </c>
-      <c r="F30" t="s">
-        <v>61</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31">
-        <v>22330051920327</v>
-      </c>
-      <c r="B31" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F31" t="s">
-        <v>61</v>
-      </c>
-      <c r="G31">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32">
-        <v>22330051920141</v>
-      </c>
-      <c r="B32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C32" t="s">
-        <v>117</v>
-      </c>
-      <c r="D32" t="s">
-        <v>153</v>
-      </c>
-      <c r="E32" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" t="s">
-        <v>61</v>
-      </c>
-      <c r="G32">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33">
-        <v>22330051920141</v>
-      </c>
-      <c r="B33" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" t="s">
-        <v>117</v>
-      </c>
-      <c r="D33" t="s">
-        <v>153</v>
-      </c>
-      <c r="E33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F33" t="s">
-        <v>61</v>
-      </c>
-      <c r="G33">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34">
-        <v>22330051920328</v>
-      </c>
-      <c r="B34" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" t="s">
-        <v>118</v>
-      </c>
-      <c r="D34" t="s">
-        <v>154</v>
-      </c>
-      <c r="E34" t="s">
-        <v>6</v>
-      </c>
-      <c r="F34" t="s">
-        <v>61</v>
-      </c>
-      <c r="G34">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35">
-        <v>22330051920328</v>
-      </c>
-      <c r="B35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C35" t="s">
-        <v>118</v>
-      </c>
-      <c r="D35" t="s">
-        <v>154</v>
-      </c>
-      <c r="E35" t="s">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>61</v>
-      </c>
-      <c r="G35">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36">
-        <v>22330051920047</v>
-      </c>
-      <c r="B36" t="s">
-        <v>93</v>
-      </c>
-      <c r="C36" t="s">
-        <v>116</v>
-      </c>
-      <c r="D36" t="s">
-        <v>155</v>
-      </c>
-      <c r="E36" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" t="s">
-        <v>61</v>
-      </c>
-      <c r="G36">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37">
-        <v>22330051920047</v>
-      </c>
-      <c r="B37" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" t="s">
-        <v>116</v>
-      </c>
-      <c r="D37" t="s">
-        <v>155</v>
-      </c>
-      <c r="E37" t="s">
-        <v>7</v>
-      </c>
-      <c r="F37" t="s">
-        <v>61</v>
-      </c>
-      <c r="G37">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38">
-        <v>22330051920198</v>
-      </c>
-      <c r="B38" t="s">
-        <v>94</v>
-      </c>
-      <c r="C38" t="s">
-        <v>119</v>
-      </c>
-      <c r="D38" t="s">
-        <v>156</v>
-      </c>
-      <c r="E38" t="s">
-        <v>6</v>
-      </c>
-      <c r="F38" t="s">
-        <v>61</v>
-      </c>
-      <c r="G38">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39">
-        <v>22330051920198</v>
-      </c>
-      <c r="B39" t="s">
-        <v>94</v>
-      </c>
-      <c r="C39" t="s">
-        <v>119</v>
-      </c>
-      <c r="D39" t="s">
-        <v>156</v>
-      </c>
-      <c r="E39" t="s">
-        <v>7</v>
-      </c>
-      <c r="F39" t="s">
-        <v>61</v>
-      </c>
-      <c r="G39">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40">
-        <v>22330051920048</v>
-      </c>
-      <c r="B40" t="s">
-        <v>95</v>
-      </c>
-      <c r="C40" t="s">
-        <v>120</v>
-      </c>
-      <c r="D40" t="s">
-        <v>157</v>
-      </c>
-      <c r="E40" t="s">
-        <v>6</v>
-      </c>
-      <c r="F40" t="s">
-        <v>61</v>
-      </c>
-      <c r="G40">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41">
-        <v>22330051920048</v>
-      </c>
-      <c r="B41" t="s">
-        <v>95</v>
-      </c>
-      <c r="C41" t="s">
-        <v>120</v>
-      </c>
-      <c r="D41" t="s">
-        <v>157</v>
-      </c>
-      <c r="E41" t="s">
-        <v>7</v>
-      </c>
-      <c r="F41" t="s">
-        <v>61</v>
-      </c>
-      <c r="G41">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42">
-        <v>22330051920329</v>
-      </c>
-      <c r="B42" t="s">
-        <v>97</v>
-      </c>
-      <c r="C42" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" t="s">
-        <v>160</v>
-      </c>
-      <c r="E42" t="s">
-        <v>6</v>
-      </c>
-      <c r="F42" t="s">
-        <v>61</v>
-      </c>
-      <c r="G42">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43">
-        <v>22330051920329</v>
-      </c>
-      <c r="B43" t="s">
-        <v>97</v>
-      </c>
-      <c r="C43" t="s">
-        <v>123</v>
-      </c>
-      <c r="D43" t="s">
-        <v>160</v>
-      </c>
-      <c r="E43" t="s">
-        <v>7</v>
-      </c>
-      <c r="F43" t="s">
-        <v>61</v>
-      </c>
-      <c r="G43">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <v>22330051920203</v>
-      </c>
-      <c r="B44" t="s">
-        <v>98</v>
-      </c>
-      <c r="C44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" t="s">
-        <v>161</v>
-      </c>
-      <c r="E44" t="s">
-        <v>6</v>
-      </c>
-      <c r="F44" t="s">
-        <v>61</v>
-      </c>
-      <c r="G44">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <v>22330051920203</v>
-      </c>
-      <c r="B45" t="s">
-        <v>98</v>
-      </c>
-      <c r="C45" t="s">
-        <v>124</v>
-      </c>
-      <c r="D45" t="s">
-        <v>161</v>
-      </c>
-      <c r="E45" t="s">
-        <v>7</v>
-      </c>
-      <c r="F45" t="s">
-        <v>61</v>
-      </c>
-      <c r="G45">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <v>22330051920050</v>
-      </c>
-      <c r="B46" t="s">
-        <v>99</v>
-      </c>
-      <c r="C46" t="s">
-        <v>125</v>
-      </c>
-      <c r="D46" t="s">
-        <v>162</v>
-      </c>
-      <c r="E46" t="s">
-        <v>6</v>
-      </c>
-      <c r="F46" t="s">
-        <v>61</v>
-      </c>
-      <c r="G46">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <v>22330051920050</v>
-      </c>
-      <c r="B47" t="s">
-        <v>99</v>
-      </c>
-      <c r="C47" t="s">
-        <v>125</v>
-      </c>
-      <c r="D47" t="s">
-        <v>162</v>
-      </c>
-      <c r="E47" t="s">
-        <v>7</v>
-      </c>
-      <c r="F47" t="s">
-        <v>61</v>
-      </c>
-      <c r="G47">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <v>22330051920051</v>
-      </c>
-      <c r="B48" t="s">
-        <v>99</v>
-      </c>
-      <c r="C48" t="s">
-        <v>126</v>
-      </c>
-      <c r="D48" t="s">
-        <v>163</v>
-      </c>
-      <c r="E48" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" t="s">
-        <v>61</v>
-      </c>
-      <c r="G48">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
-        <v>22330051920051</v>
-      </c>
-      <c r="B49" t="s">
-        <v>99</v>
-      </c>
-      <c r="C49" t="s">
-        <v>126</v>
-      </c>
-      <c r="D49" t="s">
-        <v>163</v>
-      </c>
-      <c r="E49" t="s">
-        <v>7</v>
-      </c>
-      <c r="F49" t="s">
-        <v>61</v>
-      </c>
-      <c r="G49">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="167">
   <si>
     <t>Materia</t>
   </si>
@@ -204,13 +204,22 @@
     <t>Por_Blancos</t>
   </si>
   <si>
-    <t>Desc Desc Desc</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
+    <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
     <t>NC</t>
@@ -6252,7 +6261,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>37</v>
@@ -6284,7 +6293,7 @@
         <v>10</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>37</v>
@@ -6316,7 +6325,7 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C6">
         <v>37</v>
@@ -6348,7 +6357,7 @@
         <v>7</v>
       </c>
       <c r="B7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C7">
         <v>37</v>
@@ -6391,16 +6400,16 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -6425,16 +6434,16 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>59</v>
@@ -6445,13 +6454,13 @@
         <v>22330051920029</v>
       </c>
       <c r="B2" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6462,13 +6471,13 @@
         <v>22330051920030</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D3" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -6479,13 +6488,13 @@
         <v>22330051920031</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -6496,13 +6505,13 @@
         <v>22330051920032</v>
       </c>
       <c r="B5" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D5" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -6513,13 +6522,13 @@
         <v>22330051920033</v>
       </c>
       <c r="B6" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D6" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -6530,13 +6539,13 @@
         <v>22330051920323</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -6547,13 +6556,13 @@
         <v>22330051920034</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D8" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -6564,13 +6573,13 @@
         <v>22330051920182</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -6581,13 +6590,13 @@
         <v>22330051920035</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D10" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -6598,13 +6607,13 @@
         <v>22330051920036</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D11" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -6615,13 +6624,13 @@
         <v>22330051920037</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C12" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D12" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -6632,13 +6641,13 @@
         <v>22330051920038</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="C13" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -6649,13 +6658,13 @@
         <v>22330051920331</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D14" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -6666,13 +6675,13 @@
         <v>22330051920189</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C15" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -6683,13 +6692,13 @@
         <v>22330051920039</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C16" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="D16" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -6700,13 +6709,13 @@
         <v>22330051920191</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C17" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="D17" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -6717,13 +6726,13 @@
         <v>22330051920325</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="C18" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -6734,13 +6743,13 @@
         <v>22330051920040</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="D19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -6751,13 +6760,13 @@
         <v>22330051920041</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C20" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D20" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -6768,13 +6777,13 @@
         <v>22330051920043</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C21" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D21" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -6785,13 +6794,13 @@
         <v>22330051920042</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C22" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="D22" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -6802,13 +6811,13 @@
         <v>22330051920327</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C23" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="D23" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -6819,13 +6828,13 @@
         <v>22330051920196</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C24" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="D24" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -6836,13 +6845,13 @@
         <v>22330051920044</v>
       </c>
       <c r="B25" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C25" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="D25" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -6853,13 +6862,13 @@
         <v>22330051920045</v>
       </c>
       <c r="B26" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="C26" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="D26" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -6870,13 +6879,13 @@
         <v>22330051920046</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C27" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D27" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -6887,13 +6896,13 @@
         <v>22330051920141</v>
       </c>
       <c r="B28" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C28" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D28" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -6904,13 +6913,13 @@
         <v>22330051920328</v>
       </c>
       <c r="B29" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="C29" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D29" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -6921,13 +6930,13 @@
         <v>22330051920047</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C30" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D30" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -6938,13 +6947,13 @@
         <v>22330051920198</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="D31" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -6955,13 +6964,13 @@
         <v>22330051920048</v>
       </c>
       <c r="B32" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="C32" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D32" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -6972,13 +6981,13 @@
         <v>22330051920336</v>
       </c>
       <c r="B33" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C33" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D33" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -6989,13 +6998,13 @@
         <v>22330051920049</v>
       </c>
       <c r="B34" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C34" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -7006,13 +7015,13 @@
         <v>22330051920329</v>
       </c>
       <c r="B35" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C35" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="D35" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -7023,13 +7032,13 @@
         <v>22330051920203</v>
       </c>
       <c r="B36" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -7040,13 +7049,13 @@
         <v>22330051920050</v>
       </c>
       <c r="B37" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C37" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -7057,13 +7066,13 @@
         <v>22330051920051</v>
       </c>
       <c r="B38" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C38" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -7085,16 +7094,16 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>0</v>
@@ -7111,13 +7120,13 @@
         <v>22330051920031</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -7134,13 +7143,13 @@
         <v>22330051920031</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -7157,13 +7166,13 @@
         <v>22330051920034</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7180,13 +7189,13 @@
         <v>22330051920034</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D5" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -7203,19 +7212,19 @@
         <v>22330051920189</v>
       </c>
       <c r="B6" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D6" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7226,13 +7235,13 @@
         <v>22330051920189</v>
       </c>
       <c r="B7" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="D7" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
@@ -7249,13 +7258,13 @@
         <v>22330051920043</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D8" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -7272,13 +7281,13 @@
         <v>22330051920043</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D9" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -7295,19 +7304,19 @@
         <v>22330051920049</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C10" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E10" t="s">
         <v>7</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7318,13 +7327,13 @@
         <v>22330051920049</v>
       </c>
       <c r="B11" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C11" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D11" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -7341,13 +7350,13 @@
         <v>22330051920050</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C12" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D12" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -7364,19 +7373,19 @@
         <v>22330051920050</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="C13" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="D13" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G13">
         <v>5</v>
@@ -7387,13 +7396,13 @@
         <v>22330051920035</v>
       </c>
       <c r="B14" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="C14" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D14" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="E14" t="s">
         <v>6</v>
@@ -7410,19 +7419,19 @@
         <v>22330051920036</v>
       </c>
       <c r="B15" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="C15" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="D15" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="E15" t="s">
         <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G15">
         <v>5</v>
@@ -7433,13 +7442,13 @@
         <v>22330051920141</v>
       </c>
       <c r="B16" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="D16" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="E16" t="s">
         <v>6</v>
@@ -7456,13 +7465,13 @@
         <v>22330051920047</v>
       </c>
       <c r="B17" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D17" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="E17" t="s">
         <v>6</v>
@@ -7479,19 +7488,19 @@
         <v>22330051920336</v>
       </c>
       <c r="B18" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="D18" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="E18" t="s">
         <v>5</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G18">
         <v>5</v>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -11,15 +11,14 @@
     <sheet name="Asistencias" sheetId="2" r:id="rId2"/>
     <sheet name="Totales" sheetId="3" r:id="rId3"/>
     <sheet name="Blancos" sheetId="4" r:id="rId4"/>
-    <sheet name="Totales Blanco" sheetId="5" r:id="rId5"/>
-    <sheet name="Rescatables" sheetId="6" r:id="rId6"/>
+    <sheet name="Rescatables" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -207,18 +206,18 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Garcia Felix Jose Antonio</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Garcia Felix Jose Antonio</t>
+    <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -234,28 +233,13 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVARADO</t>
-  </si>
-  <si>
-    <t>BERISTAIN</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>CRESCENCIO</t>
-  </si>
-  <si>
-    <t>CERON</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
   </si>
   <si>
     <t>GALVEZ</t>
@@ -264,79 +248,19 @@
     <t>GIL</t>
   </si>
   <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>MELCHOR</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>PALESTINO</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>TOLEDO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>XOCHICALE</t>
-  </si>
-  <si>
-    <t>YOPIHUA</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
+    <t>SALOMON</t>
   </si>
   <si>
     <t>AMAYO</t>
@@ -345,94 +269,19 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ZEPEDA</t>
-  </si>
-  <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>LOMAS</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>CRISTOBAL</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
+    <t>VIDERIQUE</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
-    <t>VIDERIQUE</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>MONGE</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>LLAVE</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>TEQUILIQUIHUA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>AXEL MICHAELL</t>
-  </si>
-  <si>
-    <t>ALVARO OZIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>SIMON</t>
-  </si>
-  <si>
-    <t>DIEGO ARMANDO</t>
-  </si>
-  <si>
-    <t>JUAN PABLO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>VECKA</t>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>DYLAN</t>
@@ -441,91 +290,19 @@
     <t>JOSE RAUL</t>
   </si>
   <si>
-    <t>FEDERICO ABIMAEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>DAMIAN</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>ALDAHIR</t>
-  </si>
-  <si>
-    <t>ERIC</t>
-  </si>
-  <si>
-    <t>ABIGAIL</t>
-  </si>
-  <si>
-    <t>KARLA ABIGAIL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>GUILLERMO JESUS</t>
-  </si>
-  <si>
-    <t>JORGE IVAN</t>
-  </si>
-  <si>
-    <t>TRISTAN YABAL</t>
-  </si>
-  <si>
-    <t>JARED ABRAHAM</t>
-  </si>
-  <si>
-    <t>JULIAN DAVID</t>
-  </si>
-  <si>
-    <t>JOSE EMMANUEL</t>
-  </si>
-  <si>
     <t>BELEN</t>
   </si>
   <si>
-    <t>OLAY</t>
-  </si>
-  <si>
     <t>ABIEL NEFTALI</t>
-  </si>
-  <si>
-    <t>ARLETT</t>
-  </si>
-  <si>
-    <t>CARLOS</t>
-  </si>
-  <si>
-    <t>CRISTINA YAJANI</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>JOSE ANTONIO</t>
-  </si>
-  <si>
-    <t>LUZ MARIA</t>
-  </si>
-  <si>
-    <t>ANGEL CHARBEL</t>
-  </si>
-  <si>
-    <t>GEOVANNI</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0\%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -578,11 +355,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1023,7 +801,7 @@
         <v>8</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -1038,7 +816,7 @@
         <v>-1</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1074,7 +852,7 @@
         <v>9</v>
       </c>
       <c r="Y4">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1100,7 +878,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -1115,7 +893,7 @@
         <v>-1</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1177,7 +955,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -1192,7 +970,7 @@
         <v>-1</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1213,7 +991,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U6">
         <v>5</v>
@@ -1228,7 +1006,7 @@
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1254,7 +1032,7 @@
         <v>10</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1269,7 +1047,7 @@
         <v>-1</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1331,7 +1109,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1346,7 +1124,7 @@
         <v>-1</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1408,7 +1186,7 @@
         <v>7</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1423,7 +1201,7 @@
         <v>-1</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1485,7 +1263,7 @@
         <v>8</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1500,7 +1278,7 @@
         <v>-1</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1521,7 +1299,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1536,7 +1314,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1562,7 +1340,7 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1577,7 +1355,7 @@
         <v>-1</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1598,7 +1376,7 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U11">
         <v>7</v>
@@ -1613,7 +1391,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1639,7 +1417,7 @@
         <v>8</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1654,7 +1432,7 @@
         <v>-1</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1675,7 +1453,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>5</v>
@@ -1716,7 +1494,7 @@
         <v>5</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1731,7 +1509,7 @@
         <v>-1</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1752,7 +1530,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1767,7 +1545,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1793,7 +1571,7 @@
         <v>8</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1808,7 +1586,7 @@
         <v>-1</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1844,7 +1622,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1870,7 +1648,7 @@
         <v>9</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1885,7 +1663,7 @@
         <v>-1</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1906,7 +1684,7 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>7</v>
@@ -1921,7 +1699,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1947,7 +1725,7 @@
         <v>7</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1962,7 +1740,7 @@
         <v>-1</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -2024,7 +1802,7 @@
         <v>7</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -2039,7 +1817,7 @@
         <v>-1</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2101,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -2116,7 +1894,7 @@
         <v>-1</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2137,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -2152,7 +1930,7 @@
         <v>5</v>
       </c>
       <c r="Y18">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2178,7 +1956,7 @@
         <v>8</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>-1</v>
@@ -2193,7 +1971,7 @@
         <v>-1</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2229,7 +2007,7 @@
         <v>9</v>
       </c>
       <c r="Y19">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2255,7 +2033,7 @@
         <v>7</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2270,7 +2048,7 @@
         <v>-1</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2306,7 +2084,7 @@
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2332,7 +2110,7 @@
         <v>10</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I21">
         <v>-1</v>
@@ -2347,7 +2125,7 @@
         <v>-1</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2383,7 +2161,7 @@
         <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2409,7 +2187,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2424,7 +2202,7 @@
         <v>-1</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2445,7 +2223,7 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U22">
         <v>6</v>
@@ -2460,7 +2238,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2486,7 +2264,7 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2501,7 +2279,7 @@
         <v>-1</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2537,7 +2315,7 @@
         <v>7</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2563,7 +2341,7 @@
         <v>6</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I24">
         <v>-1</v>
@@ -2578,7 +2356,7 @@
         <v>-1</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2599,7 +2377,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U24">
         <v>5</v>
@@ -2614,7 +2392,7 @@
         <v>6</v>
       </c>
       <c r="Y24">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:25">
@@ -2640,7 +2418,7 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I25">
         <v>-1</v>
@@ -2655,7 +2433,7 @@
         <v>-1</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2676,7 +2454,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U25">
         <v>5</v>
@@ -2691,7 +2469,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2717,7 +2495,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I26">
         <v>-1</v>
@@ -2732,7 +2510,7 @@
         <v>-1</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2794,7 +2572,7 @@
         <v>8</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I27">
         <v>-1</v>
@@ -2809,7 +2587,7 @@
         <v>-1</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2871,7 +2649,7 @@
         <v>5</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2886,7 +2664,7 @@
         <v>-1</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2907,7 +2685,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2948,7 +2726,7 @@
         <v>5</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I29">
         <v>-1</v>
@@ -2963,7 +2741,7 @@
         <v>-1</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -3025,7 +2803,7 @@
         <v>8</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I30">
         <v>-1</v>
@@ -3040,7 +2818,7 @@
         <v>-1</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3102,7 +2880,7 @@
         <v>7</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="I31">
         <v>-1</v>
@@ -3117,7 +2895,7 @@
         <v>-1</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3138,7 +2916,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="U31">
         <v>5</v>
@@ -3179,7 +2957,7 @@
         <v>7</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>-1</v>
@@ -3194,7 +2972,7 @@
         <v>-1</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3215,7 +2993,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>6</v>
@@ -3256,7 +3034,7 @@
         <v>7</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I33">
         <v>-1</v>
@@ -3271,7 +3049,7 @@
         <v>-1</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3333,7 +3111,7 @@
         <v>7</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3348,7 +3126,7 @@
         <v>-1</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
         <v>-1</v>
@@ -3369,7 +3147,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3392,7 +3170,7 @@
         <v>43</v>
       </c>
       <c r="B35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C35">
         <v>8</v>
@@ -3410,7 +3188,7 @@
         <v>8</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
         <v>-1</v>
@@ -3425,7 +3203,7 @@
         <v>-1</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3446,7 +3224,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>8</v>
@@ -3469,7 +3247,7 @@
         <v>44</v>
       </c>
       <c r="B36">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C36">
         <v>6</v>
@@ -3487,7 +3265,7 @@
         <v>7</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I36">
         <v>-1</v>
@@ -3502,7 +3280,7 @@
         <v>-1</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N36">
         <v>-1</v>
@@ -3523,7 +3301,7 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U36">
         <v>6</v>
@@ -3564,7 +3342,7 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
         <v>-1</v>
@@ -3579,7 +3357,7 @@
         <v>-1</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3641,7 +3419,7 @@
         <v>9</v>
       </c>
       <c r="H38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I38">
         <v>-1</v>
@@ -3656,7 +3434,7 @@
         <v>-1</v>
       </c>
       <c r="M38">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N38">
         <v>-1</v>
@@ -3718,7 +3496,7 @@
         <v>8</v>
       </c>
       <c r="H39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="I39">
         <v>-1</v>
@@ -3733,7 +3511,7 @@
         <v>-1</v>
       </c>
       <c r="M39">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="N39">
         <v>-1</v>
@@ -3754,7 +3532,7 @@
         <v>-1</v>
       </c>
       <c r="T39">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U39">
         <v>5</v>
@@ -3769,7 +3547,7 @@
         <v>7</v>
       </c>
       <c r="Y39">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3795,7 +3573,7 @@
         <v>9</v>
       </c>
       <c r="H40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I40">
         <v>-1</v>
@@ -3810,7 +3588,7 @@
         <v>-1</v>
       </c>
       <c r="M40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N40">
         <v>-1</v>
@@ -3846,7 +3624,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3982,7 +3760,7 @@
         <v>109.1</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3997,7 +3775,7 @@
         <v>0</v>
       </c>
       <c r="M4">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N4">
         <v>0</v>
@@ -4041,7 +3819,7 @@
         <v>109.1</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -4056,7 +3834,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N5">
         <v>0</v>
@@ -4100,7 +3878,7 @@
         <v>101.8</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -4115,7 +3893,7 @@
         <v>0</v>
       </c>
       <c r="M6">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N6">
         <v>0</v>
@@ -4159,7 +3937,7 @@
         <v>109.1</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -4174,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="M7">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N7">
         <v>0</v>
@@ -4218,7 +3996,7 @@
         <v>109.1</v>
       </c>
       <c r="H8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I8">
         <v>0</v>
@@ -4233,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N8">
         <v>0</v>
@@ -4277,7 +4055,7 @@
         <v>109.1</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -4292,7 +4070,7 @@
         <v>0</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N9">
         <v>0</v>
@@ -4336,7 +4114,7 @@
         <v>101.8</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>46.7</v>
       </c>
       <c r="I10">
         <v>0</v>
@@ -4351,7 +4129,7 @@
         <v>0</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N10">
         <v>0</v>
@@ -4395,7 +4173,7 @@
         <v>109.1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -4410,7 +4188,7 @@
         <v>0</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N11">
         <v>0</v>
@@ -4454,7 +4232,7 @@
         <v>98.2</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -4469,7 +4247,7 @@
         <v>0</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N12">
         <v>0</v>
@@ -4513,7 +4291,7 @@
         <v>98.2</v>
       </c>
       <c r="H13">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -4528,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="M13">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N13">
         <v>0</v>
@@ -4572,7 +4350,7 @@
         <v>109.1</v>
       </c>
       <c r="H14">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I14">
         <v>0</v>
@@ -4587,7 +4365,7 @@
         <v>0</v>
       </c>
       <c r="M14">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N14">
         <v>0</v>
@@ -4631,7 +4409,7 @@
         <v>109.1</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -4646,7 +4424,7 @@
         <v>0</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4690,7 +4468,7 @@
         <v>105.5</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I16">
         <v>0</v>
@@ -4705,7 +4483,7 @@
         <v>0</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4749,7 +4527,7 @@
         <v>109.1</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I17">
         <v>0</v>
@@ -4764,7 +4542,7 @@
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -4808,7 +4586,7 @@
         <v>109.1</v>
       </c>
       <c r="H18">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="I18">
         <v>0</v>
@@ -4823,7 +4601,7 @@
         <v>0</v>
       </c>
       <c r="M18">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N18">
         <v>0</v>
@@ -4867,7 +4645,7 @@
         <v>103.6</v>
       </c>
       <c r="H19">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I19">
         <v>0</v>
@@ -4882,7 +4660,7 @@
         <v>0</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N19">
         <v>0</v>
@@ -4926,7 +4704,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H20">
-        <v>0</v>
+        <v>33.3</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -4941,7 +4719,7 @@
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N20">
         <v>0</v>
@@ -4985,7 +4763,7 @@
         <v>109.1</v>
       </c>
       <c r="H21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I21">
         <v>0</v>
@@ -5000,7 +4778,7 @@
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N21">
         <v>0</v>
@@ -5044,7 +4822,7 @@
         <v>105.5</v>
       </c>
       <c r="H22">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -5059,7 +4837,7 @@
         <v>0</v>
       </c>
       <c r="M22">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N22">
         <v>0</v>
@@ -5103,7 +4881,7 @@
         <v>109.1</v>
       </c>
       <c r="H23">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I23">
         <v>0</v>
@@ -5118,7 +4896,7 @@
         <v>0</v>
       </c>
       <c r="M23">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N23">
         <v>0</v>
@@ -5162,7 +4940,7 @@
         <v>103.6</v>
       </c>
       <c r="H24">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -5177,7 +4955,7 @@
         <v>0</v>
       </c>
       <c r="M24">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N24">
         <v>0</v>
@@ -5221,7 +4999,7 @@
         <v>109.1</v>
       </c>
       <c r="H25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -5236,7 +5014,7 @@
         <v>0</v>
       </c>
       <c r="M25">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N25">
         <v>0</v>
@@ -5280,7 +5058,7 @@
         <v>101.8</v>
       </c>
       <c r="H26">
-        <v>0</v>
+        <v>53.3</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -5295,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N26">
         <v>0</v>
@@ -5339,7 +5117,7 @@
         <v>105.5</v>
       </c>
       <c r="H27">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I27">
         <v>0</v>
@@ -5354,7 +5132,7 @@
         <v>0</v>
       </c>
       <c r="M27">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N27">
         <v>0</v>
@@ -5398,7 +5176,7 @@
         <v>101.8</v>
       </c>
       <c r="H28">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I28">
         <v>0</v>
@@ -5413,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N28">
         <v>0</v>
@@ -5457,7 +5235,7 @@
         <v>98.2</v>
       </c>
       <c r="H29">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="I29">
         <v>0</v>
@@ -5472,7 +5250,7 @@
         <v>0</v>
       </c>
       <c r="M29">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N29">
         <v>0</v>
@@ -5516,7 +5294,7 @@
         <v>105.5</v>
       </c>
       <c r="H30">
-        <v>0</v>
+        <v>73.3</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -5531,7 +5309,7 @@
         <v>0</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N30">
         <v>0</v>
@@ -5575,7 +5353,7 @@
         <v>109.1</v>
       </c>
       <c r="H31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -5590,7 +5368,7 @@
         <v>0</v>
       </c>
       <c r="M31">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N31">
         <v>0</v>
@@ -5634,7 +5412,7 @@
         <v>109.1</v>
       </c>
       <c r="H32">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I32">
         <v>0</v>
@@ -5649,7 +5427,7 @@
         <v>0</v>
       </c>
       <c r="M32">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N32">
         <v>0</v>
@@ -5693,7 +5471,7 @@
         <v>100</v>
       </c>
       <c r="H33">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I33">
         <v>0</v>
@@ -5708,7 +5486,7 @@
         <v>0</v>
       </c>
       <c r="M33">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N33">
         <v>0</v>
@@ -5752,7 +5530,7 @@
         <v>109.1</v>
       </c>
       <c r="H34">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -5767,7 +5545,7 @@
         <v>0</v>
       </c>
       <c r="M34">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N34">
         <v>0</v>
@@ -5811,7 +5589,7 @@
         <v>109.1</v>
       </c>
       <c r="H35">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -5826,7 +5604,7 @@
         <v>0</v>
       </c>
       <c r="M35">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N35">
         <v>0</v>
@@ -5870,7 +5648,7 @@
         <v>96.40000000000001</v>
       </c>
       <c r="H36">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -5885,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="M36">
-        <v>0</v>
+        <v>114.5</v>
       </c>
       <c r="N36">
         <v>0</v>
@@ -5929,7 +5707,7 @@
         <v>109.1</v>
       </c>
       <c r="H37">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="I37">
         <v>0</v>
@@ -5944,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="M37">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N37">
         <v>0</v>
@@ -5988,7 +5766,7 @@
         <v>109.1</v>
       </c>
       <c r="H38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -6003,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="N38">
         <v>0</v>
@@ -6047,7 +5825,7 @@
         <v>101.8</v>
       </c>
       <c r="H39">
-        <v>0</v>
+        <v>26.7</v>
       </c>
       <c r="I39">
         <v>0</v>
@@ -6062,7 +5840,7 @@
         <v>0</v>
       </c>
       <c r="M39">
-        <v>0</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N39">
         <v>0</v>
@@ -6106,7 +5884,7 @@
         <v>109.1</v>
       </c>
       <c r="H40">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="I40">
         <v>0</v>
@@ -6121,7 +5899,7 @@
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>116.4</v>
       </c>
       <c r="N40">
         <v>0</v>
@@ -6158,6 +5936,8 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="50.7109375" customWidth="1"/>
+    <col min="6" max="7" width="9.140625" style="2"/>
+    <col min="10" max="10" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -6208,11 +5988,11 @@
       <c r="E2">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>62.16</v>
-      </c>
-      <c r="G2">
-        <v>37.84</v>
+      <c r="F2" s="2">
+        <v>62.2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>37.8</v>
       </c>
       <c r="H2">
         <v>6.2</v>
@@ -6220,13 +6000,13 @@
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6235,30 +6015,30 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="E3">
-        <v>6</v>
-      </c>
-      <c r="F3">
-        <v>83.78</v>
-      </c>
-      <c r="G3">
-        <v>16.22</v>
+        <v>11</v>
+      </c>
+      <c r="F3" s="2">
+        <v>70.3</v>
+      </c>
+      <c r="G3" s="2">
+        <v>29.7</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="I3">
         <v>0</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6267,30 +6047,30 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>5</v>
-      </c>
-      <c r="F4">
-        <v>86.48999999999999</v>
-      </c>
-      <c r="G4">
-        <v>13.51</v>
+        <v>6</v>
+      </c>
+      <c r="F4" s="2">
+        <v>83.8</v>
+      </c>
+      <c r="G4" s="2">
+        <v>16.2</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6299,30 +6079,30 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>5</v>
-      </c>
-      <c r="F5">
-        <v>86.48999999999999</v>
-      </c>
-      <c r="G5">
-        <v>13.51</v>
+        <v>4</v>
+      </c>
+      <c r="F5" s="2">
+        <v>89.2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>10.8</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6336,11 +6116,11 @@
       <c r="E6">
         <v>4</v>
       </c>
-      <c r="F6">
-        <v>89.19</v>
-      </c>
-      <c r="G6">
-        <v>10.81</v>
+      <c r="F6" s="2">
+        <v>89.2</v>
+      </c>
+      <c r="G6" s="2">
+        <v>10.8</v>
       </c>
       <c r="H6">
         <v>7.2</v>
@@ -6348,7 +6128,7 @@
       <c r="I6">
         <v>0</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6368,11 +6148,11 @@
       <c r="E7">
         <v>3</v>
       </c>
-      <c r="F7">
-        <v>91.89</v>
-      </c>
-      <c r="G7">
-        <v>8.109999999999999</v>
+      <c r="F7" s="2">
+        <v>91.90000000000001</v>
+      </c>
+      <c r="G7" s="2">
+        <v>8.1</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -6380,7 +6160,7 @@
       <c r="I7">
         <v>0</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
     </row>
@@ -6425,667 +6205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="30.7109375" customWidth="1"/>
-    <col min="2" max="4" width="50.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5">
-      <c r="A1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2">
-        <v>22330051920029</v>
-      </c>
-      <c r="B2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
-      <c r="D2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3">
-        <v>22330051920030</v>
-      </c>
-      <c r="B3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C3" t="s">
-        <v>103</v>
-      </c>
-      <c r="D3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
-        <v>22330051920031</v>
-      </c>
-      <c r="B4" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D4" t="s">
-        <v>132</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
-        <v>22330051920032</v>
-      </c>
-      <c r="B5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C5" t="s">
-        <v>92</v>
-      </c>
-      <c r="D5" t="s">
-        <v>133</v>
-      </c>
-      <c r="E5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
-        <v>22330051920033</v>
-      </c>
-      <c r="B6" t="s">
-        <v>75</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
-      </c>
-      <c r="D6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
-        <v>22330051920323</v>
-      </c>
-      <c r="B7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C7" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8">
-        <v>22330051920034</v>
-      </c>
-      <c r="B8" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" t="s">
-        <v>136</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9">
-        <v>22330051920182</v>
-      </c>
-      <c r="B9" t="s">
-        <v>78</v>
-      </c>
-      <c r="C9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10">
-        <v>22330051920035</v>
-      </c>
-      <c r="B10" t="s">
-        <v>79</v>
-      </c>
-      <c r="C10" t="s">
-        <v>106</v>
-      </c>
-      <c r="D10" t="s">
-        <v>138</v>
-      </c>
-      <c r="E10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11">
-        <v>22330051920036</v>
-      </c>
-      <c r="B11" t="s">
-        <v>80</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11" t="s">
-        <v>139</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12">
-        <v>22330051920037</v>
-      </c>
-      <c r="B12" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" t="s">
-        <v>140</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13">
-        <v>22330051920038</v>
-      </c>
-      <c r="B13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D13" t="s">
-        <v>141</v>
-      </c>
-      <c r="E13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14">
-        <v>22330051920331</v>
-      </c>
-      <c r="B14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C14" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15">
-        <v>22330051920189</v>
-      </c>
-      <c r="B15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" t="s">
-        <v>109</v>
-      </c>
-      <c r="D15" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16">
-        <v>22330051920039</v>
-      </c>
-      <c r="B16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C16" t="s">
-        <v>110</v>
-      </c>
-      <c r="D16" t="s">
-        <v>144</v>
-      </c>
-      <c r="E16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17">
-        <v>22330051920191</v>
-      </c>
-      <c r="B17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C17" t="s">
-        <v>111</v>
-      </c>
-      <c r="D17" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18">
-        <v>22330051920325</v>
-      </c>
-      <c r="B18" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19">
-        <v>22330051920040</v>
-      </c>
-      <c r="B19" t="s">
-        <v>88</v>
-      </c>
-      <c r="C19" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20">
-        <v>22330051920041</v>
-      </c>
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" t="s">
-        <v>148</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21">
-        <v>22330051920043</v>
-      </c>
-      <c r="B21" t="s">
-        <v>90</v>
-      </c>
-      <c r="C21" t="s">
-        <v>83</v>
-      </c>
-      <c r="D21" t="s">
-        <v>149</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22">
-        <v>22330051920042</v>
-      </c>
-      <c r="B22" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" t="s">
-        <v>114</v>
-      </c>
-      <c r="D22" t="s">
-        <v>150</v>
-      </c>
-      <c r="E22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23">
-        <v>22330051920327</v>
-      </c>
-      <c r="B23" t="s">
-        <v>92</v>
-      </c>
-      <c r="C23" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" t="s">
-        <v>151</v>
-      </c>
-      <c r="E23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24">
-        <v>22330051920196</v>
-      </c>
-      <c r="B24" t="s">
-        <v>93</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>152</v>
-      </c>
-      <c r="E24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25">
-        <v>22330051920044</v>
-      </c>
-      <c r="B25" t="s">
-        <v>93</v>
-      </c>
-      <c r="C25" t="s">
-        <v>117</v>
-      </c>
-      <c r="D25" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26">
-        <v>22330051920045</v>
-      </c>
-      <c r="B26" t="s">
-        <v>92</v>
-      </c>
-      <c r="C26" t="s">
-        <v>118</v>
-      </c>
-      <c r="D26" t="s">
-        <v>154</v>
-      </c>
-      <c r="E26">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27">
-        <v>22330051920046</v>
-      </c>
-      <c r="B27" t="s">
-        <v>94</v>
-      </c>
-      <c r="C27" t="s">
-        <v>119</v>
-      </c>
-      <c r="D27" t="s">
-        <v>155</v>
-      </c>
-      <c r="E27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28">
-        <v>22330051920141</v>
-      </c>
-      <c r="B28" t="s">
-        <v>94</v>
-      </c>
-      <c r="C28" t="s">
-        <v>120</v>
-      </c>
-      <c r="D28" t="s">
-        <v>156</v>
-      </c>
-      <c r="E28">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29">
-        <v>22330051920328</v>
-      </c>
-      <c r="B29" t="s">
-        <v>95</v>
-      </c>
-      <c r="C29" t="s">
-        <v>121</v>
-      </c>
-      <c r="D29" t="s">
-        <v>157</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30">
-        <v>22330051920047</v>
-      </c>
-      <c r="B30" t="s">
-        <v>96</v>
-      </c>
-      <c r="C30" t="s">
-        <v>119</v>
-      </c>
-      <c r="D30" t="s">
-        <v>158</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31">
-        <v>22330051920198</v>
-      </c>
-      <c r="B31" t="s">
-        <v>97</v>
-      </c>
-      <c r="C31" t="s">
-        <v>122</v>
-      </c>
-      <c r="D31" t="s">
-        <v>159</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32">
-        <v>22330051920048</v>
-      </c>
-      <c r="B32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C32" t="s">
-        <v>123</v>
-      </c>
-      <c r="D32" t="s">
-        <v>160</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33">
-        <v>22330051920336</v>
-      </c>
-      <c r="B33" t="s">
-        <v>99</v>
-      </c>
-      <c r="C33" t="s">
-        <v>124</v>
-      </c>
-      <c r="D33" t="s">
-        <v>161</v>
-      </c>
-      <c r="E33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34">
-        <v>22330051920049</v>
-      </c>
-      <c r="B34" t="s">
-        <v>99</v>
-      </c>
-      <c r="C34" t="s">
-        <v>125</v>
-      </c>
-      <c r="D34" t="s">
-        <v>162</v>
-      </c>
-      <c r="E34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35">
-        <v>22330051920329</v>
-      </c>
-      <c r="B35" t="s">
-        <v>100</v>
-      </c>
-      <c r="C35" t="s">
-        <v>126</v>
-      </c>
-      <c r="D35" t="s">
-        <v>163</v>
-      </c>
-      <c r="E35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36">
-        <v>22330051920203</v>
-      </c>
-      <c r="B36" t="s">
-        <v>101</v>
-      </c>
-      <c r="C36" t="s">
-        <v>127</v>
-      </c>
-      <c r="D36" t="s">
-        <v>164</v>
-      </c>
-      <c r="E36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37">
-        <v>22330051920050</v>
-      </c>
-      <c r="B37" t="s">
-        <v>102</v>
-      </c>
-      <c r="C37" t="s">
-        <v>128</v>
-      </c>
-      <c r="D37" t="s">
-        <v>165</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38">
-        <v>22330051920051</v>
-      </c>
-      <c r="B38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C38" t="s">
-        <v>129</v>
-      </c>
-      <c r="D38" t="s">
-        <v>166</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -7117,22 +6237,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920031</v>
+        <v>22330051920189</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -7140,22 +6260,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920031</v>
+        <v>22330051920189</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>85</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -7163,16 +6283,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920034</v>
+        <v>22330051920043</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -7186,22 +6306,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920034</v>
+        <v>22330051920043</v>
       </c>
       <c r="B5" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -7209,22 +6329,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920189</v>
+        <v>22330051920049</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D6" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -7232,22 +6352,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920189</v>
+        <v>22330051920049</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>109</v>
+        <v>80</v>
       </c>
       <c r="D7" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -7255,16 +6375,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920043</v>
+        <v>22330051920035</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -7278,19 +6398,19 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920043</v>
+        <v>22330051920036</v>
       </c>
       <c r="B9" t="s">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D9" t="s">
-        <v>149</v>
+        <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F9" t="s">
         <v>62</v>
@@ -7301,22 +6421,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920049</v>
+        <v>22330051920141</v>
       </c>
       <c r="B10" t="s">
-        <v>99</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
-        <v>125</v>
+        <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="E10" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G10">
         <v>5</v>
@@ -7324,185 +6444,24 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920049</v>
+        <v>22330051920047</v>
       </c>
       <c r="B11" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="C11" t="s">
-        <v>125</v>
+        <v>84</v>
       </c>
       <c r="D11" t="s">
-        <v>162</v>
+        <v>91</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920050</v>
-      </c>
-      <c r="B12" t="s">
-        <v>102</v>
-      </c>
-      <c r="C12" t="s">
-        <v>128</v>
-      </c>
-      <c r="D12" t="s">
-        <v>165</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920050</v>
-      </c>
-      <c r="B13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C13" t="s">
-        <v>128</v>
-      </c>
-      <c r="D13" t="s">
-        <v>165</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>66</v>
-      </c>
-      <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920035</v>
-      </c>
-      <c r="B14" t="s">
-        <v>79</v>
-      </c>
-      <c r="C14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" t="s">
-        <v>138</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920036</v>
-      </c>
-      <c r="B15" t="s">
-        <v>80</v>
-      </c>
-      <c r="C15" t="s">
-        <v>107</v>
-      </c>
-      <c r="D15" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>64</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920141</v>
-      </c>
-      <c r="B16" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" t="s">
-        <v>156</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>61</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920047</v>
-      </c>
-      <c r="B17" t="s">
-        <v>96</v>
-      </c>
-      <c r="C17" t="s">
-        <v>119</v>
-      </c>
-      <c r="D17" t="s">
-        <v>158</v>
-      </c>
-      <c r="E17" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" t="s">
-        <v>61</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920336</v>
-      </c>
-      <c r="B18" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" t="s">
-        <v>124</v>
-      </c>
-      <c r="D18" t="s">
-        <v>161</v>
-      </c>
-      <c r="E18" t="s">
-        <v>5</v>
-      </c>
-      <c r="F18" t="s">
-        <v>63</v>
-      </c>
-      <c r="G18">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -209,18 +209,18 @@
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,64 +233,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>JENKINS</t>
   </si>
   <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>GALVEZ</t>
-  </si>
-  <si>
     <t>GIL</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>ORTIZ</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>AMAYO</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>VIDERIQUE</t>
+    <t>ACOSTA</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
     <t>ARTHUR RICHARD</t>
   </si>
   <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>DYLAN</t>
-  </si>
-  <si>
     <t>JOSE RAUL</t>
   </si>
   <si>
-    <t>BELEN</t>
+    <t>MIGUEL ANTONIO</t>
+  </si>
+  <si>
+    <t>KARLA ABIGAIL</t>
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
@@ -804,16 +804,16 @@
         <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M4">
         <v>6</v>
@@ -849,7 +849,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -881,16 +881,16 @@
         <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M5">
         <v>9</v>
@@ -958,16 +958,16 @@
         <v>4</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M6">
         <v>5</v>
@@ -1000,7 +1000,7 @@
         <v>6</v>
       </c>
       <c r="W6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1035,16 +1035,16 @@
         <v>10</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>9</v>
@@ -1071,7 +1071,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>10</v>
@@ -1112,16 +1112,16 @@
         <v>10</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
         <v>9</v>
@@ -1148,7 +1148,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V8">
         <v>10</v>
@@ -1189,16 +1189,16 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M9">
         <v>6</v>
@@ -1234,7 +1234,7 @@
         <v>9</v>
       </c>
       <c r="X9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y9">
         <v>7</v>
@@ -1266,16 +1266,16 @@
         <v>3</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>5</v>
@@ -1308,7 +1308,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1343,16 +1343,16 @@
         <v>10</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
         <v>7</v>
@@ -1420,16 +1420,16 @@
         <v>10</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
         <v>7</v>
@@ -1456,16 +1456,16 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y12">
         <v>8</v>
@@ -1497,16 +1497,16 @@
         <v>3</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M13">
         <v>7</v>
@@ -1533,13 +1533,13 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
         <v>6</v>
       </c>
       <c r="W13">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1574,16 +1574,16 @@
         <v>10</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
         <v>6</v>
@@ -1610,13 +1610,13 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>9</v>
@@ -1651,16 +1651,16 @@
         <v>6</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
         <v>6</v>
@@ -1687,16 +1687,16 @@
         <v>8</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1728,16 +1728,16 @@
         <v>6</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M16">
         <v>6</v>
@@ -1764,13 +1764,13 @@
         <v>7</v>
       </c>
       <c r="U16">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V16">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1805,16 +1805,16 @@
         <v>6</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M17">
         <v>7</v>
@@ -1847,7 +1847,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1882,16 +1882,16 @@
         <v>4</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M18">
         <v>7</v>
@@ -1924,7 +1924,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -1959,16 +1959,16 @@
         <v>8</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M19">
         <v>6</v>
@@ -2004,7 +2004,7 @@
         <v>9</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2036,16 +2036,16 @@
         <v>3</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M20">
         <v>4</v>
@@ -2075,13 +2075,13 @@
         <v>5</v>
       </c>
       <c r="V20">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W20">
         <v>5</v>
       </c>
       <c r="X20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2113,16 +2113,16 @@
         <v>10</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M21">
         <v>7</v>
@@ -2149,16 +2149,16 @@
         <v>10</v>
       </c>
       <c r="U21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y21">
         <v>9</v>
@@ -2190,16 +2190,16 @@
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>5</v>
@@ -2226,13 +2226,13 @@
         <v>7</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V22">
         <v>6</v>
       </c>
       <c r="W22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2267,16 +2267,16 @@
         <v>10</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M23">
         <v>6</v>
@@ -2303,13 +2303,13 @@
         <v>10</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2344,16 +2344,16 @@
         <v>4</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M24">
         <v>7</v>
@@ -2389,7 +2389,7 @@
         <v>5</v>
       </c>
       <c r="X24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y24">
         <v>7</v>
@@ -2421,16 +2421,16 @@
         <v>3</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M25">
         <v>4</v>
@@ -2498,16 +2498,16 @@
         <v>4</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
         <v>4</v>
@@ -2537,7 +2537,7 @@
         <v>5</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W26">
         <v>5</v>
@@ -2575,16 +2575,16 @@
         <v>8</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M27">
         <v>7</v>
@@ -2614,13 +2614,13 @@
         <v>6</v>
       </c>
       <c r="V27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W27">
         <v>9</v>
       </c>
       <c r="X27">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y27">
         <v>8</v>
@@ -2652,16 +2652,16 @@
         <v>4</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M28">
         <v>5</v>
@@ -2694,7 +2694,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2729,16 +2729,16 @@
         <v>3</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M29">
         <v>5</v>
@@ -2771,10 +2771,10 @@
         <v>6</v>
       </c>
       <c r="W29">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2806,16 +2806,16 @@
         <v>9</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
         <v>8</v>
@@ -2842,16 +2842,16 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y30">
         <v>8</v>
@@ -2883,16 +2883,16 @@
         <v>4</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
         <v>7</v>
@@ -2925,10 +2925,10 @@
         <v>7</v>
       </c>
       <c r="W31">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X31">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -2960,16 +2960,16 @@
         <v>10</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M32">
         <v>7</v>
@@ -2996,13 +2996,13 @@
         <v>10</v>
       </c>
       <c r="U32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3037,16 +3037,16 @@
         <v>6</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M33">
         <v>7</v>
@@ -3073,16 +3073,16 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V33">
         <v>8</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y33">
         <v>7</v>
@@ -3114,16 +3114,16 @@
         <v>9</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M34">
         <v>7</v>
@@ -3153,13 +3153,13 @@
         <v>7</v>
       </c>
       <c r="V34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W34">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X34">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3191,16 +3191,16 @@
         <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M35">
         <v>8</v>
@@ -3230,10 +3230,10 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W35">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3268,16 +3268,16 @@
         <v>7</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>6</v>
@@ -3304,7 +3304,7 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V36">
         <v>5</v>
@@ -3345,16 +3345,16 @@
         <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M37">
         <v>7</v>
@@ -3381,16 +3381,16 @@
         <v>10</v>
       </c>
       <c r="U37">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W37">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="X37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y37">
         <v>8</v>
@@ -3422,16 +3422,16 @@
         <v>10</v>
       </c>
       <c r="I38">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M38">
         <v>8</v>
@@ -3461,13 +3461,13 @@
         <v>7</v>
       </c>
       <c r="V38">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W38">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X38">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="Y38">
         <v>9</v>
@@ -3499,16 +3499,16 @@
         <v>3</v>
       </c>
       <c r="I39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M39">
         <v>4</v>
@@ -3541,10 +3541,10 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="X39">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y39">
         <v>6</v>
@@ -3576,16 +3576,16 @@
         <v>8</v>
       </c>
       <c r="I40">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M40">
         <v>7</v>
@@ -3612,10 +3612,10 @@
         <v>8</v>
       </c>
       <c r="U40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V40">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3763,16 +3763,16 @@
         <v>93.3</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L4">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M4">
         <v>120</v>
@@ -3822,16 +3822,16 @@
         <v>100</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M5">
         <v>120</v>
@@ -3881,16 +3881,16 @@
         <v>80</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6">
         <v>114.5</v>
@@ -3940,16 +3940,16 @@
         <v>86.7</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M7">
         <v>120</v>
@@ -3999,16 +3999,16 @@
         <v>100</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M8">
         <v>120</v>
@@ -4058,16 +4058,16 @@
         <v>93.3</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M9">
         <v>116.4</v>
@@ -4117,16 +4117,16 @@
         <v>46.7</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M10">
         <v>114.5</v>
@@ -4176,16 +4176,16 @@
         <v>93.3</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M11">
         <v>120</v>
@@ -4235,16 +4235,16 @@
         <v>80</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M12">
         <v>120</v>
@@ -4294,16 +4294,16 @@
         <v>40</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L13">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M13">
         <v>116.4</v>
@@ -4353,16 +4353,16 @@
         <v>93.3</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L14">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M14">
         <v>120</v>
@@ -4412,16 +4412,16 @@
         <v>73.3</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M15">
         <v>120</v>
@@ -4471,16 +4471,16 @@
         <v>86.7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M16">
         <v>116.4</v>
@@ -4530,16 +4530,16 @@
         <v>100</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17">
         <v>120</v>
@@ -4589,16 +4589,16 @@
         <v>86.7</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M18">
         <v>120</v>
@@ -4648,16 +4648,16 @@
         <v>93.3</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="M19">
         <v>116.4</v>
@@ -4707,16 +4707,16 @@
         <v>33.3</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L20">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M20">
         <v>114.5</v>
@@ -4766,16 +4766,16 @@
         <v>100</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21">
         <v>120</v>
@@ -4825,16 +4825,16 @@
         <v>73.3</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J22">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="M22">
         <v>114.5</v>
@@ -4884,16 +4884,16 @@
         <v>93.3</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L23">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M23">
         <v>120</v>
@@ -4943,16 +4943,16 @@
         <v>93.3</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24">
         <v>116.4</v>
@@ -5002,16 +5002,16 @@
         <v>80</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="J25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M25">
         <v>120</v>
@@ -5061,16 +5061,16 @@
         <v>53.3</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M26">
         <v>114.5</v>
@@ -5120,16 +5120,16 @@
         <v>80</v>
       </c>
       <c r="I27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L27">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M27">
         <v>120</v>
@@ -5179,16 +5179,16 @@
         <v>80</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="M28">
         <v>120</v>
@@ -5238,16 +5238,16 @@
         <v>26.7</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J29">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="L29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M29">
         <v>114.5</v>
@@ -5297,16 +5297,16 @@
         <v>73.3</v>
       </c>
       <c r="I30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M30">
         <v>120</v>
@@ -5356,16 +5356,16 @@
         <v>100</v>
       </c>
       <c r="I31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31">
         <v>120</v>
@@ -5415,16 +5415,16 @@
         <v>93.3</v>
       </c>
       <c r="I32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32">
         <v>120</v>
@@ -5474,16 +5474,16 @@
         <v>80</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33">
         <v>116.4</v>
@@ -5533,16 +5533,16 @@
         <v>93.3</v>
       </c>
       <c r="I34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M34">
         <v>120</v>
@@ -5592,16 +5592,16 @@
         <v>93.3</v>
       </c>
       <c r="I35">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K35">
-        <v>0</v>
+        <v>105</v>
       </c>
       <c r="L35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35">
         <v>120</v>
@@ -5651,16 +5651,16 @@
         <v>80</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M36">
         <v>114.5</v>
@@ -5710,16 +5710,16 @@
         <v>93.3</v>
       </c>
       <c r="I37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M37">
         <v>120</v>
@@ -5769,16 +5769,16 @@
         <v>100</v>
       </c>
       <c r="I38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="M38">
         <v>120</v>
@@ -5828,16 +5828,16 @@
         <v>26.7</v>
       </c>
       <c r="I39">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="J39">
-        <v>0</v>
+        <v>66.7</v>
       </c>
       <c r="K39">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="L39">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="M39">
         <v>83.59999999999999</v>
@@ -5887,16 +5887,16 @@
         <v>80</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K40">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="L40">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M40">
         <v>116.4</v>
@@ -5983,19 +5983,19 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" s="2">
-        <v>62.2</v>
+        <v>59.5</v>
       </c>
       <c r="G2" s="2">
-        <v>37.8</v>
+        <v>40.5</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6047,19 +6047,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" s="2">
-        <v>83.8</v>
+        <v>86.5</v>
       </c>
       <c r="G4" s="2">
-        <v>16.2</v>
+        <v>13.5</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.3</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6079,19 +6079,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F5" s="2">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="G5" s="2">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6102,7 +6102,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6123,7 +6123,7 @@
         <v>10.8</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -6143,16 +6143,16 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F7" s="2">
-        <v>91.90000000000001</v>
+        <v>89.2</v>
       </c>
       <c r="G7" s="2">
-        <v>8.1</v>
+        <v>10.8</v>
       </c>
       <c r="H7">
         <v>7.2</v>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920189</v>
+        <v>22330051920031</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -6283,7 +6283,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920043</v>
+        <v>22330051920034</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
@@ -6295,10 +6295,10 @@
         <v>86</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6306,7 +6306,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920043</v>
+        <v>22330051920034</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
@@ -6318,10 +6318,10 @@
         <v>86</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920049</v>
+        <v>22330051920189</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -6341,10 +6341,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920049</v>
+        <v>22330051920189</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
@@ -6364,10 +6364,10 @@
         <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6375,7 +6375,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920035</v>
+        <v>22330051920036</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
@@ -6387,10 +6387,10 @@
         <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6398,7 +6398,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920036</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
@@ -6410,10 +6410,10 @@
         <v>89</v>
       </c>
       <c r="E9" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920141</v>
+        <v>22330051920041</v>
       </c>
       <c r="B10" t="s">
         <v>76</v>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -3757,10 +3757,10 @@
         <v>100</v>
       </c>
       <c r="G4">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I4">
         <v>100</v>
@@ -3769,31 +3769,31 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L4">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="M4">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N4">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S4">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" spans="1:19">
@@ -3816,7 +3816,7 @@
         <v>100</v>
       </c>
       <c r="G5">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>100</v>
@@ -3828,31 +3828,31 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
       </c>
       <c r="M5">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -3875,43 +3875,43 @@
         <v>95</v>
       </c>
       <c r="G6">
-        <v>101.8</v>
+        <v>93.3</v>
       </c>
       <c r="H6">
-        <v>80</v>
+        <v>88.3</v>
       </c>
       <c r="I6">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J6">
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L6">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M6">
-        <v>114.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N6">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="O6">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="R6">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -3934,10 +3934,10 @@
         <v>100</v>
       </c>
       <c r="G7">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H7">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I7">
         <v>100</v>
@@ -3946,31 +3946,31 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>95.2</v>
       </c>
       <c r="L7">
         <v>100</v>
       </c>
       <c r="M7">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N7">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" spans="1:19">
@@ -3993,7 +3993,7 @@
         <v>100</v>
       </c>
       <c r="G8">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H8">
         <v>100</v>
@@ -4005,31 +4005,31 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
       </c>
       <c r="M8">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -4052,43 +4052,43 @@
         <v>85</v>
       </c>
       <c r="G9">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H9">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I9">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>105</v>
+        <v>90.5</v>
       </c>
       <c r="L9">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="M9">
-        <v>116.4</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4111,43 +4111,43 @@
         <v>100</v>
       </c>
       <c r="G10">
-        <v>101.8</v>
+        <v>93.3</v>
       </c>
       <c r="H10">
-        <v>46.7</v>
+        <v>71.7</v>
       </c>
       <c r="I10">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J10">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K10">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="L10">
         <v>90</v>
       </c>
-      <c r="L10">
-        <v>80</v>
-      </c>
       <c r="M10">
-        <v>114.5</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>71.7</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4170,43 +4170,43 @@
         <v>100</v>
       </c>
       <c r="G11">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H11">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J11">
         <v>100</v>
       </c>
       <c r="K11">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L11">
+        <v>97.5</v>
+      </c>
+      <c r="M11">
+        <v>100</v>
+      </c>
+      <c r="N11">
+        <v>96.7</v>
+      </c>
+      <c r="O11">
         <v>95</v>
       </c>
-      <c r="M11">
-        <v>120</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
       <c r="P11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="12" spans="1:19">
@@ -4229,43 +4229,43 @@
         <v>75</v>
       </c>
       <c r="G12">
-        <v>98.2</v>
+        <v>90</v>
       </c>
       <c r="H12">
+        <v>86.7</v>
+      </c>
+      <c r="I12">
+        <v>85</v>
+      </c>
+      <c r="J12">
+        <v>93.3</v>
+      </c>
+      <c r="K12">
+        <v>92.90000000000001</v>
+      </c>
+      <c r="L12">
         <v>80</v>
       </c>
-      <c r="I12">
-        <v>90</v>
-      </c>
-      <c r="J12">
+      <c r="M12">
+        <v>95.2</v>
+      </c>
+      <c r="N12">
         <v>86.7</v>
       </c>
-      <c r="K12">
-        <v>110</v>
-      </c>
-      <c r="L12">
+      <c r="O12">
         <v>85</v>
       </c>
-      <c r="M12">
-        <v>120</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12">
-        <v>0</v>
-      </c>
       <c r="P12">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>95.2</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4288,43 +4288,43 @@
         <v>95</v>
       </c>
       <c r="G13">
-        <v>98.2</v>
+        <v>90</v>
       </c>
       <c r="H13">
-        <v>40</v>
+        <v>68.3</v>
       </c>
       <c r="I13">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>90</v>
+        <v>83.3</v>
       </c>
       <c r="L13">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M13">
-        <v>116.4</v>
+        <v>93.7</v>
       </c>
       <c r="N13">
-        <v>0</v>
+        <v>68.3</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="R13">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S13">
-        <v>0</v>
+        <v>93.7</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4347,10 +4347,10 @@
         <v>100</v>
       </c>
       <c r="G14">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H14">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I14">
         <v>100</v>
@@ -4359,31 +4359,31 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L14">
-        <v>85</v>
+        <v>92.5</v>
       </c>
       <c r="M14">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N14">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S14">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15" spans="1:19">
@@ -4406,43 +4406,43 @@
         <v>100</v>
       </c>
       <c r="G15">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H15">
-        <v>73.3</v>
+        <v>85</v>
       </c>
       <c r="I15">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="J15">
         <v>100</v>
       </c>
       <c r="K15">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L15">
+        <v>92.5</v>
+      </c>
+      <c r="M15">
+        <v>100</v>
+      </c>
+      <c r="N15">
         <v>85</v>
       </c>
-      <c r="M15">
-        <v>120</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
       <c r="O15">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="P15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R15">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S15">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:19">
@@ -4465,43 +4465,43 @@
         <v>100</v>
       </c>
       <c r="G16">
-        <v>105.5</v>
+        <v>96.7</v>
       </c>
       <c r="H16">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="I16">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J16">
         <v>100</v>
       </c>
       <c r="K16">
-        <v>105</v>
+        <v>90.5</v>
       </c>
       <c r="L16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M16">
-        <v>116.4</v>
+        <v>96.8</v>
       </c>
       <c r="N16">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="P16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="R16">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S16">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4524,43 +4524,43 @@
         <v>100</v>
       </c>
       <c r="G17">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H17">
-        <v>100</v>
+        <v>96.7</v>
       </c>
       <c r="I17">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J17">
         <v>100</v>
       </c>
       <c r="K17">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="L17">
         <v>100</v>
       </c>
       <c r="M17">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18" spans="1:19">
@@ -4583,10 +4583,10 @@
         <v>90</v>
       </c>
       <c r="G18">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H18">
-        <v>86.7</v>
+        <v>90</v>
       </c>
       <c r="I18">
         <v>100</v>
@@ -4595,31 +4595,31 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>90</v>
       </c>
       <c r="M18">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S18">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4642,43 +4642,43 @@
         <v>95</v>
       </c>
       <c r="G19">
-        <v>103.6</v>
+        <v>95</v>
       </c>
       <c r="H19">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I19">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J19">
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="L19">
-        <v>80</v>
+        <v>87.5</v>
       </c>
       <c r="M19">
-        <v>116.4</v>
+        <v>96</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="R19">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S19">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4701,43 +4701,43 @@
         <v>95</v>
       </c>
       <c r="G20">
-        <v>96.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="H20">
-        <v>33.3</v>
+        <v>58.3</v>
       </c>
       <c r="I20">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J20">
         <v>100</v>
       </c>
       <c r="K20">
-        <v>75</v>
+        <v>61.9</v>
       </c>
       <c r="L20">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="M20">
-        <v>114.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N20">
-        <v>0</v>
+        <v>58.3</v>
       </c>
       <c r="O20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>61.9</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4760,43 +4760,43 @@
         <v>100</v>
       </c>
       <c r="G21">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H21">
         <v>100</v>
       </c>
       <c r="I21">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J21">
         <v>100</v>
       </c>
       <c r="K21">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L21">
         <v>100</v>
       </c>
       <c r="M21">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="22" spans="1:19">
@@ -4819,43 +4819,43 @@
         <v>85</v>
       </c>
       <c r="G22">
-        <v>105.5</v>
+        <v>96.7</v>
       </c>
       <c r="H22">
-        <v>73.3</v>
+        <v>85</v>
       </c>
       <c r="I22">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J22">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L22">
-        <v>70</v>
+        <v>77.5</v>
       </c>
       <c r="M22">
-        <v>114.5</v>
+        <v>96</v>
       </c>
       <c r="N22">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="P22">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R22">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="S22">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4878,43 +4878,43 @@
         <v>100</v>
       </c>
       <c r="G23">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H23">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J23">
         <v>100</v>
       </c>
       <c r="K23">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L23">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M23">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N23">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S23">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="24" spans="1:19">
@@ -4937,43 +4937,43 @@
         <v>100</v>
       </c>
       <c r="G24">
-        <v>103.6</v>
+        <v>95</v>
       </c>
       <c r="H24">
         <v>93.3</v>
       </c>
       <c r="I24">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J24">
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>85.7</v>
       </c>
       <c r="L24">
         <v>100</v>
       </c>
       <c r="M24">
-        <v>116.4</v>
+        <v>96</v>
       </c>
       <c r="N24">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>85.7</v>
       </c>
       <c r="R24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S24">
-        <v>0</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -4996,43 +4996,43 @@
         <v>95</v>
       </c>
       <c r="G25">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H25">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="I25">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J25">
         <v>100</v>
       </c>
       <c r="K25">
-        <v>110</v>
+        <v>95.2</v>
       </c>
       <c r="L25">
         <v>95</v>
       </c>
       <c r="M25">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N25">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>95.2</v>
       </c>
       <c r="R25">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S25">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5055,43 +5055,43 @@
         <v>100</v>
       </c>
       <c r="G26">
-        <v>101.8</v>
+        <v>93.3</v>
       </c>
       <c r="H26">
-        <v>53.3</v>
+        <v>71.7</v>
       </c>
       <c r="I26">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="J26">
+        <v>90</v>
+      </c>
+      <c r="K26">
+        <v>73.8</v>
+      </c>
+      <c r="L26">
+        <v>87.5</v>
+      </c>
+      <c r="M26">
+        <v>94.40000000000001</v>
+      </c>
+      <c r="N26">
+        <v>71.7</v>
+      </c>
+      <c r="O26">
         <v>80</v>
       </c>
-      <c r="K26">
-        <v>80</v>
-      </c>
-      <c r="L26">
-        <v>75</v>
-      </c>
-      <c r="M26">
-        <v>114.5</v>
-      </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
-      <c r="O26">
-        <v>0</v>
-      </c>
       <c r="P26">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>73.8</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>87.5</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5114,43 +5114,43 @@
         <v>100</v>
       </c>
       <c r="G27">
-        <v>105.5</v>
+        <v>96.7</v>
       </c>
       <c r="H27">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I27">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J27">
         <v>100</v>
       </c>
       <c r="K27">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="L27">
+        <v>97.5</v>
+      </c>
+      <c r="M27">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="N27">
+        <v>90</v>
+      </c>
+      <c r="O27">
         <v>95</v>
       </c>
-      <c r="M27">
-        <v>120</v>
-      </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
-      <c r="O27">
-        <v>0</v>
-      </c>
       <c r="P27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S27">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5173,43 +5173,43 @@
         <v>60</v>
       </c>
       <c r="G28">
-        <v>101.8</v>
+        <v>93.3</v>
       </c>
       <c r="H28">
-        <v>80</v>
+        <v>86.7</v>
       </c>
       <c r="I28">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J28">
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>90.5</v>
       </c>
       <c r="L28">
-        <v>85</v>
+        <v>72.5</v>
       </c>
       <c r="M28">
-        <v>120</v>
+        <v>96.8</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>86.7</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="P28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>90.5</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>72.5</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>96.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5232,43 +5232,43 @@
         <v>90</v>
       </c>
       <c r="G29">
-        <v>98.2</v>
+        <v>90</v>
       </c>
       <c r="H29">
-        <v>26.7</v>
+        <v>60</v>
       </c>
       <c r="I29">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J29">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="K29">
-        <v>70</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="L29">
         <v>90</v>
       </c>
       <c r="M29">
-        <v>114.5</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="N29">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O29">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="R29">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="S29">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5291,10 +5291,10 @@
         <v>60</v>
       </c>
       <c r="G30">
-        <v>105.5</v>
+        <v>96.7</v>
       </c>
       <c r="H30">
-        <v>73.3</v>
+        <v>83.3</v>
       </c>
       <c r="I30">
         <v>90</v>
@@ -5303,31 +5303,31 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L30">
-        <v>95</v>
+        <v>77.5</v>
       </c>
       <c r="M30">
-        <v>120</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5350,7 +5350,7 @@
         <v>100</v>
       </c>
       <c r="G31">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H31">
         <v>100</v>
@@ -5362,31 +5362,31 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L31">
         <v>100</v>
       </c>
       <c r="M31">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S31">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:19">
@@ -5409,10 +5409,10 @@
         <v>100</v>
       </c>
       <c r="G32">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H32">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I32">
         <v>100</v>
@@ -5421,31 +5421,31 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L32">
         <v>100</v>
       </c>
       <c r="M32">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N32">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S32">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:19">
@@ -5468,43 +5468,43 @@
         <v>95</v>
       </c>
       <c r="G33">
-        <v>100</v>
+        <v>91.7</v>
       </c>
       <c r="H33">
-        <v>80</v>
+        <v>88.3</v>
       </c>
       <c r="I33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J33">
-        <v>86.7</v>
+        <v>93.3</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L33">
-        <v>100</v>
+        <v>97.5</v>
       </c>
       <c r="M33">
-        <v>116.4</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="N33">
-        <v>0</v>
+        <v>88.3</v>
       </c>
       <c r="O33">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="R33">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S33">
-        <v>0</v>
+        <v>94.40000000000001</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5527,7 +5527,7 @@
         <v>100</v>
       </c>
       <c r="G34">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H34">
         <v>93.3</v>
@@ -5539,31 +5539,31 @@
         <v>100</v>
       </c>
       <c r="K34">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L34">
         <v>100</v>
       </c>
       <c r="M34">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N34">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q34">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R34">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S34">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:19">
@@ -5586,43 +5586,43 @@
         <v>100</v>
       </c>
       <c r="G35">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H35">
         <v>93.3</v>
       </c>
       <c r="I35">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J35">
         <v>100</v>
       </c>
       <c r="K35">
-        <v>105</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L35">
         <v>100</v>
       </c>
       <c r="M35">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N35">
-        <v>0</v>
+        <v>93.3</v>
       </c>
       <c r="O35">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q35">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R35">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="S35">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:19">
@@ -5645,43 +5645,43 @@
         <v>90</v>
       </c>
       <c r="G36">
-        <v>96.40000000000001</v>
+        <v>88.3</v>
       </c>
       <c r="H36">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I36">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="J36">
         <v>100</v>
       </c>
       <c r="K36">
-        <v>95</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="L36">
-        <v>95</v>
+        <v>92.5</v>
       </c>
       <c r="M36">
-        <v>114.5</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="N36">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="O36">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="P36">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q36">
-        <v>0</v>
+        <v>88.09999999999999</v>
       </c>
       <c r="R36">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S36">
-        <v>0</v>
+        <v>92.09999999999999</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5704,43 +5704,43 @@
         <v>100</v>
       </c>
       <c r="G37">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H37">
-        <v>93.3</v>
+        <v>96.7</v>
       </c>
       <c r="I37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J37">
         <v>100</v>
       </c>
       <c r="K37">
-        <v>110</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="L37">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="M37">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N37">
-        <v>0</v>
+        <v>96.7</v>
       </c>
       <c r="O37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P37">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q37">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R37">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="S37">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:19">
@@ -5763,43 +5763,43 @@
         <v>95</v>
       </c>
       <c r="G38">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H38">
         <v>100</v>
       </c>
       <c r="I38">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J38">
         <v>100</v>
       </c>
       <c r="K38">
-        <v>110</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="L38">
-        <v>90</v>
+        <v>92.5</v>
       </c>
       <c r="M38">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="P38">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q38">
-        <v>0</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>92.5</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:19">
@@ -5822,43 +5822,43 @@
         <v>90</v>
       </c>
       <c r="G39">
-        <v>101.8</v>
+        <v>93.3</v>
       </c>
       <c r="H39">
-        <v>26.7</v>
+        <v>60</v>
       </c>
       <c r="I39">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="J39">
-        <v>66.7</v>
+        <v>83.3</v>
       </c>
       <c r="K39">
-        <v>75</v>
+        <v>76.2</v>
       </c>
       <c r="L39">
-        <v>35</v>
+        <v>62.5</v>
       </c>
       <c r="M39">
-        <v>83.59999999999999</v>
+        <v>81</v>
       </c>
       <c r="N39">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="O39">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="P39">
-        <v>0</v>
+        <v>83.3</v>
       </c>
       <c r="Q39">
-        <v>0</v>
+        <v>76.2</v>
       </c>
       <c r="R39">
-        <v>0</v>
+        <v>62.5</v>
       </c>
       <c r="S39">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -5881,43 +5881,43 @@
         <v>100</v>
       </c>
       <c r="G40">
-        <v>109.1</v>
+        <v>100</v>
       </c>
       <c r="H40">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="I40">
+        <v>95</v>
+      </c>
+      <c r="J40">
+        <v>100</v>
+      </c>
+      <c r="K40">
+        <v>97.59999999999999</v>
+      </c>
+      <c r="L40">
+        <v>97.5</v>
+      </c>
+      <c r="M40">
+        <v>98.40000000000001</v>
+      </c>
+      <c r="N40">
         <v>90</v>
       </c>
-      <c r="J40">
-        <v>100</v>
-      </c>
-      <c r="K40">
-        <v>110</v>
-      </c>
-      <c r="L40">
+      <c r="O40">
         <v>95</v>
       </c>
-      <c r="M40">
-        <v>116.4</v>
-      </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
-      <c r="O40">
-        <v>0</v>
-      </c>
       <c r="P40">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="Q40">
-        <v>0</v>
+        <v>97.59999999999999</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>97.5</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>98.40000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
   <si>
     <t>Materia</t>
   </si>
@@ -209,12 +209,12 @@
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
+    <t>Rosas Aguilar Claudia Leonor</t>
+  </si>
+  <si>
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Rosas Aguilar Claudia Leonor</t>
-  </si>
-  <si>
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
@@ -233,64 +233,64 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>JENKINS</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
-    <t>GIL</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>ORTIZ</t>
-  </si>
-  <si>
     <t>ROBLES</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ZEPEDA</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>ACOSTA</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>ARTHUR RICHARD</t>
+  </si>
+  <si>
+    <t>ROGGER JUSEFH</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
     <t>RICARDO</t>
   </si>
   <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
-  </si>
-  <si>
     <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>KARLA ABIGAIL</t>
   </si>
   <si>
     <t>ABIEL NEFTALI</t>
@@ -819,13 +819,13 @@
         <v>6</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O4">
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
         <v>-1</v>
@@ -896,13 +896,13 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O5">
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q5">
         <v>-1</v>
@@ -920,7 +920,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>10</v>
@@ -973,13 +973,13 @@
         <v>5</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q6">
         <v>-1</v>
@@ -991,13 +991,13 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>5</v>
       </c>
       <c r="V6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W6">
         <v>6</v>
@@ -1050,13 +1050,13 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
         <v>-1</v>
@@ -1127,13 +1127,13 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
         <v>-1</v>
@@ -1204,13 +1204,13 @@
         <v>6</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q9">
         <v>-1</v>
@@ -1222,13 +1222,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U9">
         <v>7</v>
       </c>
       <c r="V9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W9">
         <v>9</v>
@@ -1281,13 +1281,13 @@
         <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O10">
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q10">
         <v>-1</v>
@@ -1358,13 +1358,13 @@
         <v>7</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O11">
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q11">
         <v>-1</v>
@@ -1376,13 +1376,13 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U11">
         <v>7</v>
       </c>
       <c r="V11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>10</v>
@@ -1435,13 +1435,13 @@
         <v>7</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O12">
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q12">
         <v>-1</v>
@@ -1459,7 +1459,7 @@
         <v>7</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1512,13 +1512,13 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q13">
         <v>-1</v>
@@ -1530,7 +1530,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
         <v>6</v>
@@ -1589,13 +1589,13 @@
         <v>6</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O14">
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
         <v>-1</v>
@@ -1613,7 +1613,7 @@
         <v>8</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W14">
         <v>9</v>
@@ -1666,13 +1666,13 @@
         <v>6</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O15">
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
         <v>-1</v>
@@ -1743,13 +1743,13 @@
         <v>6</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O16">
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q16">
         <v>-1</v>
@@ -1761,7 +1761,7 @@
         <v>-1</v>
       </c>
       <c r="T16">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U16">
         <v>5</v>
@@ -1820,13 +1820,13 @@
         <v>7</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q17">
         <v>-1</v>
@@ -1897,13 +1897,13 @@
         <v>7</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>-1</v>
@@ -1915,7 +1915,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
         <v>5</v>
@@ -1974,13 +1974,13 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O19">
         <v>-1</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q19">
         <v>-1</v>
@@ -1992,13 +1992,13 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U19">
         <v>7</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
         <v>9</v>
@@ -2051,13 +2051,13 @@
         <v>4</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O20">
         <v>-1</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q20">
         <v>-1</v>
@@ -2128,13 +2128,13 @@
         <v>7</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O21">
         <v>-1</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
         <v>-1</v>
@@ -2205,13 +2205,13 @@
         <v>5</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O22">
         <v>-1</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
         <v>-1</v>
@@ -2223,13 +2223,13 @@
         <v>-1</v>
       </c>
       <c r="T22">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U22">
         <v>5</v>
       </c>
       <c r="V22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2282,13 +2282,13 @@
         <v>6</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O23">
         <v>-1</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q23">
         <v>-1</v>
@@ -2300,7 +2300,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
         <v>8</v>
@@ -2359,13 +2359,13 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O24">
         <v>-1</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q24">
         <v>-1</v>
@@ -2377,13 +2377,13 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24">
         <v>5</v>
       </c>
       <c r="V24">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W24">
         <v>5</v>
@@ -2436,13 +2436,13 @@
         <v>4</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O25">
         <v>-1</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q25">
         <v>-1</v>
@@ -2513,13 +2513,13 @@
         <v>4</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O26">
         <v>-1</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
         <v>-1</v>
@@ -2590,13 +2590,13 @@
         <v>7</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O27">
         <v>-1</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q27">
         <v>-1</v>
@@ -2608,7 +2608,7 @@
         <v>-1</v>
       </c>
       <c r="T27">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="U27">
         <v>6</v>
@@ -2667,13 +2667,13 @@
         <v>5</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O28">
         <v>-1</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q28">
         <v>-1</v>
@@ -2685,7 +2685,7 @@
         <v>-1</v>
       </c>
       <c r="T28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U28">
         <v>5</v>
@@ -2744,13 +2744,13 @@
         <v>5</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O29">
         <v>-1</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q29">
         <v>-1</v>
@@ -2768,7 +2768,7 @@
         <v>5</v>
       </c>
       <c r="V29">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W29">
         <v>7</v>
@@ -2821,13 +2821,13 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O30">
         <v>-1</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q30">
         <v>-1</v>
@@ -2845,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="V30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2898,13 +2898,13 @@
         <v>7</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O31">
         <v>-1</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q31">
         <v>-1</v>
@@ -2975,13 +2975,13 @@
         <v>7</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O32">
         <v>-1</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q32">
         <v>-1</v>
@@ -2993,13 +2993,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U32">
         <v>7</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W32">
         <v>10</v>
@@ -3052,13 +3052,13 @@
         <v>7</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O33">
         <v>-1</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q33">
         <v>-1</v>
@@ -3129,13 +3129,13 @@
         <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O34">
         <v>-1</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q34">
         <v>-1</v>
@@ -3147,7 +3147,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U34">
         <v>7</v>
@@ -3206,13 +3206,13 @@
         <v>8</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
         <v>-1</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q35">
         <v>-1</v>
@@ -3230,7 +3230,7 @@
         <v>8</v>
       </c>
       <c r="V35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W35">
         <v>8</v>
@@ -3283,13 +3283,13 @@
         <v>6</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O36">
         <v>-1</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q36">
         <v>-1</v>
@@ -3307,7 +3307,7 @@
         <v>5</v>
       </c>
       <c r="V36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W36">
         <v>5</v>
@@ -3360,13 +3360,13 @@
         <v>7</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O37">
         <v>-1</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
         <v>-1</v>
@@ -3378,7 +3378,7 @@
         <v>-1</v>
       </c>
       <c r="T37">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U37">
         <v>7</v>
@@ -3437,13 +3437,13 @@
         <v>8</v>
       </c>
       <c r="N38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O38">
         <v>-1</v>
       </c>
       <c r="P38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q38">
         <v>-1</v>
@@ -3514,13 +3514,13 @@
         <v>4</v>
       </c>
       <c r="N39">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="O39">
         <v>-1</v>
       </c>
       <c r="P39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q39">
         <v>-1</v>
@@ -3591,13 +3591,13 @@
         <v>7</v>
       </c>
       <c r="N40">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O40">
         <v>-1</v>
       </c>
       <c r="P40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q40">
         <v>-1</v>
@@ -3615,7 +3615,7 @@
         <v>7</v>
       </c>
       <c r="V40">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W40">
         <v>9</v>
@@ -3896,7 +3896,7 @@
         <v>94.40000000000001</v>
       </c>
       <c r="N6">
-        <v>88.3</v>
+        <v>90</v>
       </c>
       <c r="O6">
         <v>65</v>
@@ -3955,7 +3955,7 @@
         <v>100</v>
       </c>
       <c r="N7">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O7">
         <v>100</v>
@@ -4073,13 +4073,13 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N9">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O9">
         <v>95</v>
       </c>
       <c r="P9">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Q9">
         <v>90.5</v>
@@ -4132,13 +4132,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="N10">
-        <v>71.7</v>
+        <v>76.7</v>
       </c>
       <c r="O10">
         <v>85</v>
       </c>
       <c r="P10">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="Q10">
         <v>78.59999999999999</v>
@@ -4191,7 +4191,7 @@
         <v>100</v>
       </c>
       <c r="N11">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O11">
         <v>95</v>
@@ -4250,13 +4250,13 @@
         <v>95.2</v>
       </c>
       <c r="N12">
-        <v>86.7</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O12">
         <v>85</v>
       </c>
       <c r="P12">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Q12">
         <v>92.90000000000001</v>
@@ -4309,7 +4309,7 @@
         <v>93.7</v>
       </c>
       <c r="N13">
-        <v>68.3</v>
+        <v>80</v>
       </c>
       <c r="O13">
         <v>85</v>
@@ -4427,7 +4427,7 @@
         <v>100</v>
       </c>
       <c r="N15">
-        <v>85</v>
+        <v>87.8</v>
       </c>
       <c r="O15">
         <v>87.5</v>
@@ -4486,7 +4486,7 @@
         <v>96.8</v>
       </c>
       <c r="N16">
-        <v>93.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O16">
         <v>75</v>
@@ -4545,7 +4545,7 @@
         <v>100</v>
       </c>
       <c r="N17">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O17">
         <v>90</v>
@@ -4604,7 +4604,7 @@
         <v>100</v>
       </c>
       <c r="N18">
-        <v>90</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O18">
         <v>100</v>
@@ -4663,7 +4663,7 @@
         <v>96</v>
       </c>
       <c r="N19">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O19">
         <v>90</v>
@@ -4722,13 +4722,13 @@
         <v>92.09999999999999</v>
       </c>
       <c r="N20">
-        <v>58.3</v>
+        <v>52.2</v>
       </c>
       <c r="O20">
         <v>85</v>
       </c>
       <c r="P20">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="Q20">
         <v>61.9</v>
@@ -4781,7 +4781,7 @@
         <v>100</v>
       </c>
       <c r="N21">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O21">
         <v>95</v>
@@ -4840,13 +4840,13 @@
         <v>96</v>
       </c>
       <c r="N22">
-        <v>85</v>
+        <v>56.7</v>
       </c>
       <c r="O22">
         <v>80</v>
       </c>
       <c r="P22">
-        <v>93.3</v>
+        <v>62.5</v>
       </c>
       <c r="Q22">
         <v>92.90000000000001</v>
@@ -4899,7 +4899,7 @@
         <v>100</v>
       </c>
       <c r="N23">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O23">
         <v>95</v>
@@ -4958,7 +4958,7 @@
         <v>96</v>
       </c>
       <c r="N24">
-        <v>93.3</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O24">
         <v>95</v>
@@ -5023,7 +5023,7 @@
         <v>85</v>
       </c>
       <c r="P25">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Q25">
         <v>95.2</v>
@@ -5076,13 +5076,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="N26">
-        <v>71.7</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="O26">
         <v>80</v>
       </c>
       <c r="P26">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q26">
         <v>73.8</v>
@@ -5135,7 +5135,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N27">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O27">
         <v>95</v>
@@ -5253,13 +5253,13 @@
         <v>92.90000000000001</v>
       </c>
       <c r="N29">
-        <v>60</v>
+        <v>62.2</v>
       </c>
       <c r="O29">
         <v>85</v>
       </c>
       <c r="P29">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="Q29">
         <v>78.59999999999999</v>
@@ -5312,7 +5312,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N30">
-        <v>83.3</v>
+        <v>86.7</v>
       </c>
       <c r="O30">
         <v>90</v>
@@ -5371,13 +5371,13 @@
         <v>100</v>
       </c>
       <c r="N31">
-        <v>100</v>
+        <v>97.8</v>
       </c>
       <c r="O31">
         <v>100</v>
       </c>
       <c r="P31">
-        <v>100</v>
+        <v>95.8</v>
       </c>
       <c r="Q31">
         <v>97.59999999999999</v>
@@ -5430,7 +5430,7 @@
         <v>100</v>
       </c>
       <c r="N32">
-        <v>96.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O32">
         <v>100</v>
@@ -5489,13 +5489,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="N33">
-        <v>88.3</v>
+        <v>90</v>
       </c>
       <c r="O33">
         <v>95</v>
       </c>
       <c r="P33">
-        <v>93.3</v>
+        <v>95.8</v>
       </c>
       <c r="Q33">
         <v>88.09999999999999</v>
@@ -5548,7 +5548,7 @@
         <v>100</v>
       </c>
       <c r="N34">
-        <v>93.3</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="O34">
         <v>100</v>
@@ -5607,7 +5607,7 @@
         <v>100</v>
       </c>
       <c r="N35">
-        <v>93.3</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O35">
         <v>95</v>
@@ -5666,7 +5666,7 @@
         <v>92.09999999999999</v>
       </c>
       <c r="N36">
-        <v>90</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="O36">
         <v>85</v>
@@ -5725,7 +5725,7 @@
         <v>100</v>
       </c>
       <c r="N37">
-        <v>96.7</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="O37">
         <v>95</v>
@@ -5784,7 +5784,7 @@
         <v>100</v>
       </c>
       <c r="N38">
-        <v>100</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="O38">
         <v>95</v>
@@ -5843,13 +5843,13 @@
         <v>81</v>
       </c>
       <c r="N39">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O39">
         <v>65</v>
       </c>
       <c r="P39">
-        <v>83.3</v>
+        <v>52.1</v>
       </c>
       <c r="Q39">
         <v>76.2</v>
@@ -5902,7 +5902,7 @@
         <v>98.40000000000001</v>
       </c>
       <c r="N40">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="O40">
         <v>95</v>
@@ -6015,19 +6015,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2">
-        <v>70.3</v>
+        <v>75.7</v>
       </c>
       <c r="G3" s="2">
-        <v>29.7</v>
+        <v>24.3</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6038,7 +6038,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6047,19 +6047,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" s="2">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
       <c r="G4" s="2">
-        <v>13.5</v>
+        <v>16.2</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6070,7 +6070,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6091,7 +6091,7 @@
         <v>13.5</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6205,7 +6205,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6237,7 +6237,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920031</v>
+        <v>22330051920034</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -6260,7 +6260,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920031</v>
+        <v>22330051920034</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
@@ -6283,7 +6283,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
@@ -6306,7 +6306,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920034</v>
+        <v>22330051920189</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
@@ -6329,7 +6329,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
@@ -6341,10 +6341,10 @@
         <v>87</v>
       </c>
       <c r="E6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6352,7 +6352,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
@@ -6364,10 +6364,10 @@
         <v>87</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6375,7 +6375,7 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920036</v>
+        <v>22330051920049</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
@@ -6387,10 +6387,10 @@
         <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -6398,22 +6398,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920038</v>
+        <v>22330051920049</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C9" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6421,16 +6421,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920041</v>
+        <v>22330051920031</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6444,16 +6444,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920047</v>
+        <v>22330051920038</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C11" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E11" t="s">
         <v>6</v>
@@ -6462,6 +6462,29 @@
         <v>61</v>
       </c>
       <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920047</v>
+      </c>
+      <c r="B12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C12" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" t="s">
+        <v>91</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="89">
   <si>
     <t>Materia</t>
   </si>
@@ -209,6 +209,9 @@
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
+    <t>Zarate Amezcua Eladio Jorge</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
@@ -218,9 +221,6 @@
     <t>Moreno Aroyo Anél</t>
   </si>
   <si>
-    <t>Zarate Amezcua Eladio Jorge</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,9 +236,6 @@
     <t>CRUZ</t>
   </si>
   <si>
-    <t>JENKINS</t>
-  </si>
-  <si>
     <t>LUNA</t>
   </si>
   <si>
@@ -257,9 +254,6 @@
     <t>REYES</t>
   </si>
   <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
@@ -276,9 +270,6 @@
   </si>
   <si>
     <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>ARTHUR RICHARD</t>
   </si>
   <si>
     <t>ROGGER JUSEFH</t>
@@ -834,7 +825,7 @@
         <v>-1</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>9</v>
@@ -911,7 +902,7 @@
         <v>-1</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -988,7 +979,7 @@
         <v>-1</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
         <v>7</v>
@@ -1065,7 +1056,7 @@
         <v>-1</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1142,7 +1133,7 @@
         <v>-1</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1219,7 +1210,7 @@
         <v>-1</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>8</v>
@@ -1237,7 +1228,7 @@
         <v>7</v>
       </c>
       <c r="Y9">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1296,7 +1287,7 @@
         <v>-1</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T10">
         <v>5</v>
@@ -1314,7 +1305,7 @@
         <v>6</v>
       </c>
       <c r="Y10">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1373,7 +1364,7 @@
         <v>-1</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T11">
         <v>9</v>
@@ -1391,7 +1382,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1450,7 +1441,7 @@
         <v>-1</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
@@ -1527,7 +1518,7 @@
         <v>-1</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
         <v>6</v>
@@ -1545,7 +1536,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1604,7 +1595,7 @@
         <v>-1</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>10</v>
@@ -1622,7 +1613,7 @@
         <v>9</v>
       </c>
       <c r="Y14">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1681,7 +1672,7 @@
         <v>-1</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
         <v>8</v>
@@ -1699,7 +1690,7 @@
         <v>8</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1758,7 +1749,7 @@
         <v>-1</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T16">
         <v>6</v>
@@ -1776,7 +1767,7 @@
         <v>6</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1835,7 +1826,7 @@
         <v>-1</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="T17">
         <v>5</v>
@@ -1853,7 +1844,7 @@
         <v>6</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1912,7 +1903,7 @@
         <v>-1</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T18">
         <v>6</v>
@@ -1989,7 +1980,7 @@
         <v>-1</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>8</v>
@@ -2066,7 +2057,7 @@
         <v>-1</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T20">
         <v>5</v>
@@ -2143,7 +2134,7 @@
         <v>-1</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T21">
         <v>10</v>
@@ -2161,7 +2152,7 @@
         <v>8</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2220,7 +2211,7 @@
         <v>-1</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T22">
         <v>5</v>
@@ -2238,7 +2229,7 @@
         <v>6</v>
       </c>
       <c r="Y22">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2297,7 +2288,7 @@
         <v>-1</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T23">
         <v>9</v>
@@ -2374,7 +2365,7 @@
         <v>-1</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T24">
         <v>5</v>
@@ -2451,7 +2442,7 @@
         <v>-1</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="T25">
         <v>5</v>
@@ -2469,7 +2460,7 @@
         <v>5</v>
       </c>
       <c r="Y25">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2528,7 +2519,7 @@
         <v>-1</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2605,7 +2596,7 @@
         <v>-1</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>7</v>
@@ -2682,7 +2673,7 @@
         <v>-1</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T28">
         <v>6</v>
@@ -2759,7 +2750,7 @@
         <v>-1</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T29">
         <v>5</v>
@@ -2836,7 +2827,7 @@
         <v>-1</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>9</v>
@@ -2854,7 +2845,7 @@
         <v>8</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2913,7 +2904,7 @@
         <v>-1</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T31">
         <v>6</v>
@@ -2990,7 +2981,7 @@
         <v>-1</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T32">
         <v>9</v>
@@ -3008,7 +2999,7 @@
         <v>8</v>
       </c>
       <c r="Y32">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3067,7 +3058,7 @@
         <v>-1</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T33">
         <v>7</v>
@@ -3085,7 +3076,7 @@
         <v>7</v>
       </c>
       <c r="Y33">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3144,7 +3135,7 @@
         <v>-1</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
         <v>8</v>
@@ -3221,7 +3212,7 @@
         <v>-1</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3239,7 +3230,7 @@
         <v>8</v>
       </c>
       <c r="Y35">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:25">
@@ -3298,7 +3289,7 @@
         <v>-1</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T36">
         <v>6</v>
@@ -3375,7 +3366,7 @@
         <v>-1</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T37">
         <v>9</v>
@@ -3452,7 +3443,7 @@
         <v>-1</v>
       </c>
       <c r="S38">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T38">
         <v>10</v>
@@ -3529,7 +3520,7 @@
         <v>-1</v>
       </c>
       <c r="S39">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="T39">
         <v>5</v>
@@ -3547,7 +3538,7 @@
         <v>6</v>
       </c>
       <c r="Y39">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:25">
@@ -3606,7 +3597,7 @@
         <v>-1</v>
       </c>
       <c r="S40">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T40">
         <v>8</v>
@@ -3624,7 +3615,7 @@
         <v>8</v>
       </c>
       <c r="Y40">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3911,7 +3902,7 @@
         <v>97.5</v>
       </c>
       <c r="S6">
-        <v>94.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -4088,7 +4079,7 @@
         <v>87.5</v>
       </c>
       <c r="S9">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="10" spans="1:19">
@@ -4147,7 +4138,7 @@
         <v>90</v>
       </c>
       <c r="S10">
-        <v>94.40000000000001</v>
+        <v>93.40000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:19">
@@ -4265,7 +4256,7 @@
         <v>80</v>
       </c>
       <c r="S12">
-        <v>95.2</v>
+        <v>96.7</v>
       </c>
     </row>
     <row r="13" spans="1:19">
@@ -4324,7 +4315,7 @@
         <v>85</v>
       </c>
       <c r="S13">
-        <v>93.7</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="14" spans="1:19">
@@ -4501,7 +4492,7 @@
         <v>95</v>
       </c>
       <c r="S16">
-        <v>96.8</v>
+        <v>95</v>
       </c>
     </row>
     <row r="17" spans="1:19">
@@ -4678,7 +4669,7 @@
         <v>87.5</v>
       </c>
       <c r="S19">
-        <v>96</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="20" spans="1:19">
@@ -4737,7 +4728,7 @@
         <v>85</v>
       </c>
       <c r="S20">
-        <v>92.09999999999999</v>
+        <v>86.2</v>
       </c>
     </row>
     <row r="21" spans="1:19">
@@ -4855,7 +4846,7 @@
         <v>77.5</v>
       </c>
       <c r="S22">
-        <v>96</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:19">
@@ -4973,7 +4964,7 @@
         <v>100</v>
       </c>
       <c r="S24">
-        <v>96</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="25" spans="1:19">
@@ -5032,7 +5023,7 @@
         <v>95</v>
       </c>
       <c r="S25">
-        <v>100</v>
+        <v>97.2</v>
       </c>
     </row>
     <row r="26" spans="1:19">
@@ -5091,7 +5082,7 @@
         <v>87.5</v>
       </c>
       <c r="S26">
-        <v>94.40000000000001</v>
+        <v>87.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -5150,7 +5141,7 @@
         <v>97.5</v>
       </c>
       <c r="S27">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:19">
@@ -5209,7 +5200,7 @@
         <v>72.5</v>
       </c>
       <c r="S28">
-        <v>96.8</v>
+        <v>97.8</v>
       </c>
     </row>
     <row r="29" spans="1:19">
@@ -5268,7 +5259,7 @@
         <v>90</v>
       </c>
       <c r="S29">
-        <v>92.90000000000001</v>
+        <v>81.2</v>
       </c>
     </row>
     <row r="30" spans="1:19">
@@ -5327,7 +5318,7 @@
         <v>77.5</v>
       </c>
       <c r="S30">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:19">
@@ -5504,7 +5495,7 @@
         <v>97.5</v>
       </c>
       <c r="S33">
-        <v>94.40000000000001</v>
+        <v>96.09999999999999</v>
       </c>
     </row>
     <row r="34" spans="1:19">
@@ -5681,7 +5672,7 @@
         <v>92.5</v>
       </c>
       <c r="S36">
-        <v>92.09999999999999</v>
+        <v>94.5</v>
       </c>
     </row>
     <row r="37" spans="1:19">
@@ -5858,7 +5849,7 @@
         <v>62.5</v>
       </c>
       <c r="S39">
-        <v>81</v>
+        <v>78.5</v>
       </c>
     </row>
     <row r="40" spans="1:19">
@@ -5917,7 +5908,7 @@
         <v>97.5</v>
       </c>
       <c r="S40">
-        <v>98.40000000000001</v>
+        <v>98.90000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -6038,7 +6029,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6047,19 +6038,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F4" s="2">
-        <v>83.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G4" s="2">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6070,7 +6061,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6079,19 +6070,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F5" s="2">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
       <c r="G5" s="2">
-        <v>13.5</v>
+        <v>16.2</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6102,7 +6093,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6111,19 +6102,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="G6" s="2">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6134,7 +6125,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -6155,7 +6146,7 @@
         <v>10.8</v>
       </c>
       <c r="H7">
-        <v>7.2</v>
+        <v>8.1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6205,7 +6196,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6243,10 +6234,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -6266,10 +6257,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>6</v>
@@ -6283,22 +6274,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6306,22 +6297,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920189</v>
+        <v>22330051920039</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6329,16 +6320,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920039</v>
+        <v>22330051920049</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -6352,22 +6343,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920039</v>
+        <v>22330051920049</v>
       </c>
       <c r="B7" t="s">
         <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G7">
         <v>5</v>
@@ -6375,16 +6366,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920049</v>
+        <v>22330051920031</v>
       </c>
       <c r="B8" t="s">
         <v>74</v>
       </c>
       <c r="C8" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -6398,22 +6389,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920049</v>
+        <v>22330051920038</v>
       </c>
       <c r="B9" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C9" t="s">
         <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="G9">
         <v>5</v>
@@ -6421,16 +6412,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920031</v>
+        <v>22330051920047</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C10" t="s">
         <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -6439,52 +6430,6 @@
         <v>61</v>
       </c>
       <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920038</v>
-      </c>
-      <c r="B11" t="s">
-        <v>76</v>
-      </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>90</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>61</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920047</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D12" t="s">
-        <v>91</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>61</v>
-      </c>
-      <c r="G12">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
   <si>
     <t>Materia</t>
   </si>
@@ -206,6 +206,9 @@
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
+    <t>Moreno Aroyo Anél</t>
+  </si>
+  <si>
     <t>Garcia Felix Jose Antonio</t>
   </si>
   <si>
@@ -218,9 +221,6 @@
     <t>García Sánchez Magda Bexabe</t>
   </si>
   <si>
-    <t>Moreno Aroyo Anél</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -233,58 +233,31 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>CRUZ</t>
+    <t>CASTILLO</t>
   </si>
   <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>REYES</t>
+    <t>GIL</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
   </si>
   <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ACOSTA</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
   </si>
   <si>
     <t>ROGGER JUSEFH</t>
   </si>
   <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANTONIO</t>
-  </si>
-  <si>
-    <t>ABIEL NEFTALI</t>
+    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -813,13 +786,13 @@
         <v>9</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
         <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -890,13 +863,13 @@
         <v>10</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P5">
         <v>7</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -908,7 +881,7 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>9</v>
@@ -967,13 +940,13 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
         <v>8</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -991,7 +964,7 @@
         <v>7</v>
       </c>
       <c r="W6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X6">
         <v>7</v>
@@ -1044,13 +1017,13 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P7">
         <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1121,13 +1094,13 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P8">
         <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1198,13 +1171,13 @@
         <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
         <v>8</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1216,13 +1189,13 @@
         <v>8</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>7</v>
       </c>
       <c r="W9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>7</v>
@@ -1275,13 +1248,13 @@
         <v>5</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P10">
         <v>6</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1299,7 +1272,7 @@
         <v>6</v>
       </c>
       <c r="W10">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X10">
         <v>6</v>
@@ -1352,13 +1325,13 @@
         <v>9</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P11">
         <v>7</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1370,13 +1343,13 @@
         <v>9</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V11">
         <v>8</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>10</v>
@@ -1429,13 +1402,13 @@
         <v>9</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
         <v>6</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1453,7 +1426,7 @@
         <v>7</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X12">
         <v>8</v>
@@ -1506,13 +1479,13 @@
         <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P13">
         <v>6</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1530,7 +1503,7 @@
         <v>6</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X13">
         <v>7</v>
@@ -1583,13 +1556,13 @@
         <v>9</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
         <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1601,7 +1574,7 @@
         <v>10</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>8</v>
@@ -1660,13 +1633,13 @@
         <v>7</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1684,7 +1657,7 @@
         <v>9</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X15">
         <v>8</v>
@@ -1737,13 +1710,13 @@
         <v>6</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
         <v>6</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1755,13 +1728,13 @@
         <v>6</v>
       </c>
       <c r="U16">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V16">
         <v>6</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X16">
         <v>6</v>
@@ -1814,13 +1787,13 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
         <v>6</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1838,7 +1811,7 @@
         <v>6</v>
       </c>
       <c r="W17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>6</v>
@@ -1891,13 +1864,13 @@
         <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
         <v>6</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -1915,7 +1888,7 @@
         <v>6</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X18">
         <v>5</v>
@@ -1968,13 +1941,13 @@
         <v>8</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P19">
         <v>8</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
         <v>-1</v>
@@ -1986,13 +1959,13 @@
         <v>8</v>
       </c>
       <c r="U19">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>8</v>
@@ -2045,13 +2018,13 @@
         <v>3</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P20">
         <v>5</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R20">
         <v>-1</v>
@@ -2122,13 +2095,13 @@
         <v>10</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P21">
         <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R21">
         <v>-1</v>
@@ -2146,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>8</v>
@@ -2199,13 +2172,13 @@
         <v>3</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
         <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R22">
         <v>-1</v>
@@ -2223,7 +2196,7 @@
         <v>5</v>
       </c>
       <c r="W22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X22">
         <v>6</v>
@@ -2276,13 +2249,13 @@
         <v>8</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P23">
         <v>10</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R23">
         <v>-1</v>
@@ -2300,7 +2273,7 @@
         <v>10</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
         <v>7</v>
@@ -2353,13 +2326,13 @@
         <v>5</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P24">
         <v>6</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R24">
         <v>-1</v>
@@ -2430,13 +2403,13 @@
         <v>3</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P25">
         <v>5</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R25">
         <v>-1</v>
@@ -2454,7 +2427,7 @@
         <v>5</v>
       </c>
       <c r="W25">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X25">
         <v>5</v>
@@ -2507,13 +2480,13 @@
         <v>6</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P26">
         <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R26">
         <v>-1</v>
@@ -2584,13 +2557,13 @@
         <v>4</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P27">
         <v>7</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R27">
         <v>-1</v>
@@ -2608,7 +2581,7 @@
         <v>7</v>
       </c>
       <c r="W27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X27">
         <v>7</v>
@@ -2661,13 +2634,13 @@
         <v>8</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
         <v>7</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R28">
         <v>-1</v>
@@ -2685,7 +2658,7 @@
         <v>6</v>
       </c>
       <c r="W28">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="X28">
         <v>5</v>
@@ -2738,13 +2711,13 @@
         <v>3</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P29">
         <v>5</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R29">
         <v>-1</v>
@@ -2762,7 +2735,7 @@
         <v>5</v>
       </c>
       <c r="W29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X29">
         <v>7</v>
@@ -2815,13 +2788,13 @@
         <v>9</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P30">
         <v>6</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R30">
         <v>-1</v>
@@ -2833,13 +2806,13 @@
         <v>9</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
         <v>7</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X30">
         <v>8</v>
@@ -2892,13 +2865,13 @@
         <v>6</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P31">
         <v>7</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R31">
         <v>-1</v>
@@ -2910,13 +2883,13 @@
         <v>6</v>
       </c>
       <c r="U31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V31">
         <v>7</v>
       </c>
       <c r="W31">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -2969,13 +2942,13 @@
         <v>8</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P32">
         <v>8</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
         <v>-1</v>
@@ -2993,7 +2966,7 @@
         <v>8</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X32">
         <v>8</v>
@@ -3046,13 +3019,13 @@
         <v>7</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
         <v>7</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
         <v>-1</v>
@@ -3064,7 +3037,7 @@
         <v>7</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V33">
         <v>8</v>
@@ -3123,13 +3096,13 @@
         <v>6</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P34">
         <v>8</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R34">
         <v>-1</v>
@@ -3147,7 +3120,7 @@
         <v>7</v>
       </c>
       <c r="W34">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X34">
         <v>7</v>
@@ -3200,13 +3173,13 @@
         <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
         <v>10</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R35">
         <v>-1</v>
@@ -3218,13 +3191,13 @@
         <v>10</v>
       </c>
       <c r="U35">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V35">
         <v>9</v>
       </c>
       <c r="W35">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X35">
         <v>8</v>
@@ -3277,13 +3250,13 @@
         <v>6</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
         <v>7</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R36">
         <v>-1</v>
@@ -3295,13 +3268,13 @@
         <v>6</v>
       </c>
       <c r="U36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V36">
         <v>6</v>
       </c>
       <c r="W36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X36">
         <v>7</v>
@@ -3354,13 +3327,13 @@
         <v>6</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P37">
         <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R37">
         <v>-1</v>
@@ -3378,7 +3351,7 @@
         <v>8</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>8</v>
@@ -3431,13 +3404,13 @@
         <v>10</v>
       </c>
       <c r="O38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P38">
         <v>10</v>
       </c>
       <c r="Q38">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R38">
         <v>-1</v>
@@ -3455,7 +3428,7 @@
         <v>9</v>
       </c>
       <c r="W38">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X38">
         <v>8</v>
@@ -3508,13 +3481,13 @@
         <v>3</v>
       </c>
       <c r="O39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P39">
         <v>5</v>
       </c>
       <c r="Q39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R39">
         <v>-1</v>
@@ -3532,7 +3505,7 @@
         <v>5</v>
       </c>
       <c r="W39">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="X39">
         <v>6</v>
@@ -3585,13 +3558,13 @@
         <v>9</v>
       </c>
       <c r="O40">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P40">
         <v>7</v>
       </c>
       <c r="Q40">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R40">
         <v>-1</v>
@@ -3609,7 +3582,7 @@
         <v>7</v>
       </c>
       <c r="W40">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X40">
         <v>8</v>
@@ -3837,7 +3810,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3890,13 +3863,13 @@
         <v>90</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="P6">
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R6">
         <v>97.5</v>
@@ -3955,7 +3928,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>95.2</v>
+        <v>95.3</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -4067,13 +4040,13 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="P9">
         <v>95.8</v>
       </c>
       <c r="Q9">
-        <v>90.5</v>
+        <v>92.2</v>
       </c>
       <c r="R9">
         <v>87.5</v>
@@ -4126,13 +4099,13 @@
         <v>76.7</v>
       </c>
       <c r="O10">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P10">
         <v>87.5</v>
       </c>
       <c r="Q10">
-        <v>78.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="R10">
         <v>90</v>
@@ -4185,13 +4158,13 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O11">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P11">
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="R11">
         <v>97.5</v>
@@ -4244,13 +4217,13 @@
         <v>88.90000000000001</v>
       </c>
       <c r="O12">
-        <v>85</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P12">
         <v>95.8</v>
       </c>
       <c r="Q12">
-        <v>92.90000000000001</v>
+        <v>92.2</v>
       </c>
       <c r="R12">
         <v>80</v>
@@ -4303,13 +4276,13 @@
         <v>80</v>
       </c>
       <c r="O13">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>83.3</v>
+        <v>79.7</v>
       </c>
       <c r="R13">
         <v>85</v>
@@ -4362,13 +4335,13 @@
         <v>96.7</v>
       </c>
       <c r="O14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="P14">
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>100</v>
+        <v>93.8</v>
       </c>
       <c r="R14">
         <v>92.5</v>
@@ -4421,13 +4394,13 @@
         <v>87.8</v>
       </c>
       <c r="O15">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="P15">
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="R15">
         <v>92.5</v>
@@ -4480,13 +4453,13 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O16">
-        <v>75</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="P16">
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>90.5</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="R16">
         <v>95</v>
@@ -4539,13 +4512,13 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O17">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P17">
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>95.2</v>
+        <v>92.2</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4604,7 +4577,7 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="R18">
         <v>90</v>
@@ -4657,13 +4630,13 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O19">
-        <v>90</v>
+        <v>93.8</v>
       </c>
       <c r="P19">
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>90.5</v>
+        <v>87.5</v>
       </c>
       <c r="R19">
         <v>87.5</v>
@@ -4716,13 +4689,13 @@
         <v>52.2</v>
       </c>
       <c r="O20">
-        <v>85</v>
+        <v>68.8</v>
       </c>
       <c r="P20">
         <v>93.8</v>
       </c>
       <c r="Q20">
-        <v>61.9</v>
+        <v>42.2</v>
       </c>
       <c r="R20">
         <v>85</v>
@@ -4775,13 +4748,13 @@
         <v>98.90000000000001</v>
       </c>
       <c r="O21">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P21">
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>97.59999999999999</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4834,13 +4807,13 @@
         <v>56.7</v>
       </c>
       <c r="O22">
-        <v>80</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="P22">
         <v>62.5</v>
       </c>
       <c r="Q22">
-        <v>92.90000000000001</v>
+        <v>60.9</v>
       </c>
       <c r="R22">
         <v>77.5</v>
@@ -4893,13 +4866,13 @@
         <v>95.59999999999999</v>
       </c>
       <c r="O23">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P23">
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="R23">
         <v>95</v>
@@ -4952,13 +4925,13 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O24">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P24">
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>85.7</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -5011,13 +4984,13 @@
         <v>86.7</v>
       </c>
       <c r="O25">
-        <v>85</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="P25">
         <v>95.8</v>
       </c>
       <c r="Q25">
-        <v>95.2</v>
+        <v>93.8</v>
       </c>
       <c r="R25">
         <v>95</v>
@@ -5070,13 +5043,13 @@
         <v>78.90000000000001</v>
       </c>
       <c r="O26">
-        <v>80</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="P26">
         <v>93.8</v>
       </c>
       <c r="Q26">
-        <v>73.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="R26">
         <v>87.5</v>
@@ -5129,13 +5102,13 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O27">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P27">
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>100</v>
+        <v>95.3</v>
       </c>
       <c r="R27">
         <v>97.5</v>
@@ -5188,13 +5161,13 @@
         <v>86.7</v>
       </c>
       <c r="O28">
-        <v>55</v>
+        <v>62.5</v>
       </c>
       <c r="P28">
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>90.5</v>
+        <v>87.5</v>
       </c>
       <c r="R28">
         <v>72.5</v>
@@ -5247,13 +5220,13 @@
         <v>62.2</v>
       </c>
       <c r="O29">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="P29">
         <v>93.8</v>
       </c>
       <c r="Q29">
-        <v>78.59999999999999</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="R29">
         <v>90</v>
@@ -5306,13 +5279,13 @@
         <v>86.7</v>
       </c>
       <c r="O30">
-        <v>90</v>
+        <v>87.5</v>
       </c>
       <c r="P30">
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>97.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="R30">
         <v>77.5</v>
@@ -5371,7 +5344,7 @@
         <v>95.8</v>
       </c>
       <c r="Q31">
-        <v>97.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -5430,7 +5403,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5483,13 +5456,13 @@
         <v>90</v>
       </c>
       <c r="O33">
-        <v>95</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="P33">
         <v>95.8</v>
       </c>
       <c r="Q33">
-        <v>88.09999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="R33">
         <v>97.5</v>
@@ -5548,7 +5521,7 @@
         <v>100</v>
       </c>
       <c r="Q34">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R34">
         <v>100</v>
@@ -5601,13 +5574,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="O35">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="P35">
         <v>100</v>
       </c>
       <c r="Q35">
-        <v>97.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="R35">
         <v>100</v>
@@ -5660,13 +5633,13 @@
         <v>91.09999999999999</v>
       </c>
       <c r="O36">
-        <v>85</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="P36">
         <v>100</v>
       </c>
       <c r="Q36">
-        <v>88.09999999999999</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="R36">
         <v>92.5</v>
@@ -5719,13 +5692,13 @@
         <v>94.40000000000001</v>
       </c>
       <c r="O37">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P37">
         <v>100</v>
       </c>
       <c r="Q37">
-        <v>97.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="R37">
         <v>95</v>
@@ -5778,13 +5751,13 @@
         <v>98.90000000000001</v>
       </c>
       <c r="O38">
-        <v>95</v>
+        <v>93.8</v>
       </c>
       <c r="P38">
         <v>100</v>
       </c>
       <c r="Q38">
-        <v>92.90000000000001</v>
+        <v>93.8</v>
       </c>
       <c r="R38">
         <v>92.5</v>
@@ -5837,13 +5810,13 @@
         <v>40</v>
       </c>
       <c r="O39">
-        <v>65</v>
+        <v>56.3</v>
       </c>
       <c r="P39">
         <v>52.1</v>
       </c>
       <c r="Q39">
-        <v>76.2</v>
+        <v>50</v>
       </c>
       <c r="R39">
         <v>62.5</v>
@@ -5896,13 +5869,13 @@
         <v>92.2</v>
       </c>
       <c r="O40">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="P40">
         <v>100</v>
       </c>
       <c r="Q40">
-        <v>97.59999999999999</v>
+        <v>93.8</v>
       </c>
       <c r="R40">
         <v>97.5</v>
@@ -5974,16 +5947,16 @@
         <v>37</v>
       </c>
       <c r="D2">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2" s="2">
-        <v>59.5</v>
+        <v>67.59999999999999</v>
       </c>
       <c r="G2" s="2">
-        <v>40.5</v>
+        <v>32.4</v>
       </c>
       <c r="H2">
         <v>6.4</v>
@@ -5997,7 +5970,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
         <v>62</v>
@@ -6018,7 +5991,7 @@
         <v>24.3</v>
       </c>
       <c r="H3">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -6029,7 +6002,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
         <v>63</v>
@@ -6038,19 +6011,19 @@
         <v>37</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E4">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F4" s="2">
-        <v>78.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="G4" s="2">
-        <v>21.6</v>
+        <v>24.3</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -6061,7 +6034,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>64</v>
@@ -6070,19 +6043,19 @@
         <v>37</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F5" s="2">
-        <v>83.8</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="G5" s="2">
-        <v>16.2</v>
+        <v>21.6</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -6093,7 +6066,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6102,19 +6075,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F6" s="2">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
       <c r="G6" s="2">
-        <v>13.5</v>
+        <v>16.2</v>
       </c>
       <c r="H6">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6125,7 +6098,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -6134,19 +6107,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2">
-        <v>89.2</v>
+        <v>86.5</v>
       </c>
       <c r="G7" s="2">
-        <v>10.8</v>
+        <v>13.5</v>
       </c>
       <c r="H7">
-        <v>8.1</v>
+        <v>7.3</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6196,7 +6169,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6228,22 +6201,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920034</v>
+        <v>22330051920031</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
       </c>
       <c r="C2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" t="s">
         <v>77</v>
       </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6251,22 +6224,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920034</v>
+        <v>22330051920031</v>
       </c>
       <c r="B3" t="s">
         <v>71</v>
       </c>
       <c r="C3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D3" t="s">
         <v>77</v>
       </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
       <c r="E3" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -6280,10 +6253,10 @@
         <v>72</v>
       </c>
       <c r="C4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" t="s">
         <v>78</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6303,16 +6276,16 @@
         <v>72</v>
       </c>
       <c r="C5" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" t="s">
         <v>78</v>
       </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
       <c r="E5" t="s">
         <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6320,116 +6293,24 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920049</v>
+        <v>22330051920036</v>
       </c>
       <c r="B6" t="s">
         <v>73</v>
       </c>
       <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
         <v>79</v>
       </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920049</v>
-      </c>
-      <c r="B7" t="s">
-        <v>73</v>
-      </c>
-      <c r="C7" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>66</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920031</v>
-      </c>
-      <c r="B8" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>61</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920038</v>
-      </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
-      <c r="C9" t="s">
-        <v>81</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920047</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>61</v>
-      </c>
-      <c r="G10">
         <v>5</v>
       </c>
     </row>

--- a/grupos/2BEM - Estadisticos 20222.xlsx
+++ b/grupos/2BEM - Estadisticos 20222.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="83">
   <si>
     <t>Materia</t>
   </si>
@@ -215,12 +215,12 @@
     <t>Zarate Amezcua Eladio Jorge</t>
   </si>
   <si>
+    <t>García Sánchez Magda Bexabe</t>
+  </si>
+  <si>
     <t>Rosas Aguilar Claudia Leonor</t>
   </si>
   <si>
-    <t>García Sánchez Magda Bexabe</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -236,28 +236,37 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>GIL</t>
+  </si>
+  <si>
     <t>LUNA</t>
   </si>
   <si>
-    <t>GIL</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
     <t>ZEPEDA</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
     <t>RICARDO</t>
   </si>
   <si>
+    <t>JULIAN DAVID</t>
+  </si>
+  <si>
+    <t>JOSE RAUL</t>
+  </si>
+  <si>
     <t>ROGGER JUSEFH</t>
-  </si>
-  <si>
-    <t>JOSE RAUL</t>
   </si>
 </sst>
 </file>
@@ -795,7 +804,7 @@
         <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S4">
         <v>6</v>
@@ -813,7 +822,7 @@
         <v>10</v>
       </c>
       <c r="X4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>7</v>
@@ -872,7 +881,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>9</v>
@@ -949,7 +958,7 @@
         <v>5</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
         <v>9</v>
@@ -1026,7 +1035,7 @@
         <v>10</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
         <v>10</v>
@@ -1103,7 +1112,7 @@
         <v>10</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
         <v>10</v>
@@ -1180,7 +1189,7 @@
         <v>7</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
         <v>6</v>
@@ -1198,7 +1207,7 @@
         <v>8</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y9">
         <v>6</v>
@@ -1257,7 +1266,7 @@
         <v>5</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
         <v>5</v>
@@ -1334,7 +1343,7 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
         <v>10</v>
@@ -1352,7 +1361,7 @@
         <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>9</v>
@@ -1411,7 +1420,7 @@
         <v>7</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S12">
         <v>10</v>
@@ -1488,7 +1497,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
         <v>8</v>
@@ -1565,7 +1574,7 @@
         <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S14">
         <v>10</v>
@@ -1583,7 +1592,7 @@
         <v>9</v>
       </c>
       <c r="X14">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>8</v>
@@ -1642,7 +1651,7 @@
         <v>8</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S15">
         <v>7</v>
@@ -1660,7 +1669,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1719,7 +1728,7 @@
         <v>5</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S16">
         <v>5</v>
@@ -1796,7 +1805,7 @@
         <v>5</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S17">
         <v>3</v>
@@ -1873,7 +1882,7 @@
         <v>5</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S18">
         <v>6</v>
@@ -1891,7 +1900,7 @@
         <v>7</v>
       </c>
       <c r="X18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y18">
         <v>6</v>
@@ -1950,7 +1959,7 @@
         <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
         <v>8</v>
@@ -1968,7 +1977,7 @@
         <v>8</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y19">
         <v>7</v>
@@ -2027,7 +2036,7 @@
         <v>5</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S20">
         <v>2</v>
@@ -2045,7 +2054,7 @@
         <v>5</v>
       </c>
       <c r="X20">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y20">
         <v>5</v>
@@ -2104,7 +2113,7 @@
         <v>7</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S21">
         <v>8</v>
@@ -2122,7 +2131,7 @@
         <v>8</v>
       </c>
       <c r="X21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y21">
         <v>8</v>
@@ -2181,7 +2190,7 @@
         <v>5</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
         <v>2</v>
@@ -2199,7 +2208,7 @@
         <v>5</v>
       </c>
       <c r="X22">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y22">
         <v>5</v>
@@ -2258,7 +2267,7 @@
         <v>7</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S23">
         <v>8</v>
@@ -2335,7 +2344,7 @@
         <v>6</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S24">
         <v>7</v>
@@ -2412,7 +2421,7 @@
         <v>5</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S25">
         <v>4</v>
@@ -2489,7 +2498,7 @@
         <v>5</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S26">
         <v>5</v>
@@ -2566,7 +2575,7 @@
         <v>7</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S27">
         <v>10</v>
@@ -2643,7 +2652,7 @@
         <v>5</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
         <v>6</v>
@@ -2661,7 +2670,7 @@
         <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
         <v>5</v>
@@ -2720,7 +2729,7 @@
         <v>5</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="S29">
         <v>2</v>
@@ -2738,7 +2747,7 @@
         <v>5</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Y29">
         <v>5</v>
@@ -2797,7 +2806,7 @@
         <v>6</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S30">
         <v>10</v>
@@ -2874,7 +2883,7 @@
         <v>5</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S31">
         <v>7</v>
@@ -2892,7 +2901,7 @@
         <v>7</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y31">
         <v>7</v>
@@ -2951,7 +2960,7 @@
         <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S32">
         <v>9</v>
@@ -2969,7 +2978,7 @@
         <v>8</v>
       </c>
       <c r="X32">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y32">
         <v>8</v>
@@ -3028,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S33">
         <v>10</v>
@@ -3105,7 +3114,7 @@
         <v>6</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S34">
         <v>8</v>
@@ -3123,7 +3132,7 @@
         <v>8</v>
       </c>
       <c r="X34">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y34">
         <v>7</v>
@@ -3182,7 +3191,7 @@
         <v>6</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S35">
         <v>10</v>
@@ -3259,7 +3268,7 @@
         <v>8</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
         <v>7</v>
@@ -3277,7 +3286,7 @@
         <v>6</v>
       </c>
       <c r="X36">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y36">
         <v>7</v>
@@ -3336,7 +3345,7 @@
         <v>6</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S37">
         <v>10</v>
@@ -3413,7 +3422,7 @@
         <v>9</v>
       </c>
       <c r="R38">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S38">
         <v>10</v>
@@ -3490,7 +3499,7 @@
         <v>5</v>
       </c>
       <c r="R39">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S39">
         <v>2</v>
@@ -3508,7 +3517,7 @@
         <v>5</v>
       </c>
       <c r="X39">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y39">
         <v>5</v>
@@ -3567,7 +3576,7 @@
         <v>5</v>
       </c>
       <c r="R40">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S40">
         <v>10</v>
@@ -3754,7 +3763,7 @@
         <v>100</v>
       </c>
       <c r="R4">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S4">
         <v>100</v>
@@ -3872,7 +3881,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="R6">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S6">
         <v>96.09999999999999</v>
@@ -3990,7 +3999,7 @@
         <v>100</v>
       </c>
       <c r="R8">
-        <v>100</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S8">
         <v>100</v>
@@ -4049,7 +4058,7 @@
         <v>92.2</v>
       </c>
       <c r="R9">
-        <v>87.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S9">
         <v>98.90000000000001</v>
@@ -4108,7 +4117,7 @@
         <v>79.7</v>
       </c>
       <c r="R10">
-        <v>90</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="S10">
         <v>93.40000000000001</v>
@@ -4167,7 +4176,7 @@
         <v>96.90000000000001</v>
       </c>
       <c r="R11">
-        <v>97.5</v>
+        <v>95.3</v>
       </c>
       <c r="S11">
         <v>100</v>
@@ -4226,7 +4235,7 @@
         <v>92.2</v>
       </c>
       <c r="R12">
-        <v>80</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S12">
         <v>96.7</v>
@@ -4285,7 +4294,7 @@
         <v>79.7</v>
       </c>
       <c r="R13">
-        <v>85</v>
+        <v>87.5</v>
       </c>
       <c r="S13">
         <v>95.59999999999999</v>
@@ -4344,7 +4353,7 @@
         <v>93.8</v>
       </c>
       <c r="R14">
-        <v>92.5</v>
+        <v>90.59999999999999</v>
       </c>
       <c r="S14">
         <v>100</v>
@@ -4403,7 +4412,7 @@
         <v>95.3</v>
       </c>
       <c r="R15">
-        <v>92.5</v>
+        <v>93.8</v>
       </c>
       <c r="S15">
         <v>100</v>
@@ -4462,7 +4471,7 @@
         <v>89.09999999999999</v>
       </c>
       <c r="R16">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S16">
         <v>95</v>
@@ -4580,7 +4589,7 @@
         <v>95.3</v>
       </c>
       <c r="R18">
-        <v>90</v>
+        <v>92.2</v>
       </c>
       <c r="S18">
         <v>100</v>
@@ -4698,7 +4707,7 @@
         <v>42.2</v>
       </c>
       <c r="R20">
-        <v>85</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="S20">
         <v>86.2</v>
@@ -4816,7 +4825,7 @@
         <v>60.9</v>
       </c>
       <c r="R22">
-        <v>77.5</v>
+        <v>48.4</v>
       </c>
       <c r="S22">
         <v>89</v>
@@ -4875,7 +4884,7 @@
         <v>95.3</v>
       </c>
       <c r="R23">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S23">
         <v>100</v>
@@ -4934,7 +4943,7 @@
         <v>85.90000000000001</v>
       </c>
       <c r="R24">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S24">
         <v>97.2</v>
@@ -4993,7 +5002,7 @@
         <v>93.8</v>
       </c>
       <c r="R25">
-        <v>95</v>
+        <v>92.2</v>
       </c>
       <c r="S25">
         <v>97.2</v>
@@ -5052,7 +5061,7 @@
         <v>71.90000000000001</v>
       </c>
       <c r="R26">
-        <v>87.5</v>
+        <v>82.8</v>
       </c>
       <c r="S26">
         <v>87.8</v>
@@ -5111,7 +5120,7 @@
         <v>95.3</v>
       </c>
       <c r="R27">
-        <v>97.5</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S27">
         <v>98.90000000000001</v>
@@ -5170,7 +5179,7 @@
         <v>87.5</v>
       </c>
       <c r="R28">
-        <v>72.5</v>
+        <v>81.3</v>
       </c>
       <c r="S28">
         <v>97.8</v>
@@ -5229,7 +5238,7 @@
         <v>73.40000000000001</v>
       </c>
       <c r="R29">
-        <v>90</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="S29">
         <v>81.2</v>
@@ -5288,7 +5297,7 @@
         <v>93.8</v>
       </c>
       <c r="R30">
-        <v>77.5</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="S30">
         <v>98.90000000000001</v>
@@ -5347,7 +5356,7 @@
         <v>95.3</v>
       </c>
       <c r="R31">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S31">
         <v>100</v>
@@ -5465,7 +5474,7 @@
         <v>87.5</v>
       </c>
       <c r="R33">
-        <v>97.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="S33">
         <v>96.09999999999999</v>
@@ -5583,7 +5592,7 @@
         <v>93.8</v>
       </c>
       <c r="R35">
-        <v>100</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="S35">
         <v>100</v>
@@ -5642,7 +5651,7 @@
         <v>90.59999999999999</v>
       </c>
       <c r="R36">
-        <v>92.5</v>
+        <v>92.2</v>
       </c>
       <c r="S36">
         <v>94.5</v>
@@ -5701,7 +5710,7 @@
         <v>93.8</v>
       </c>
       <c r="R37">
-        <v>95</v>
+        <v>95.3</v>
       </c>
       <c r="S37">
         <v>100</v>
@@ -5760,7 +5769,7 @@
         <v>93.8</v>
       </c>
       <c r="R38">
-        <v>92.5</v>
+        <v>95.3</v>
       </c>
       <c r="S38">
         <v>100</v>
@@ -5819,7 +5828,7 @@
         <v>50</v>
       </c>
       <c r="R39">
-        <v>62.5</v>
+        <v>39.1</v>
       </c>
       <c r="S39">
         <v>78.5</v>
@@ -5878,7 +5887,7 @@
         <v>93.8</v>
       </c>
       <c r="R40">
-        <v>97.5</v>
+        <v>93.8</v>
       </c>
       <c r="S40">
         <v>98.90000000000001</v>
@@ -6066,7 +6075,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>65</v>
@@ -6075,19 +6084,19 @@
         <v>37</v>
       </c>
       <c r="D6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F6" s="2">
-        <v>83.8</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="G6" s="2">
-        <v>16.2</v>
+        <v>18.9</v>
       </c>
       <c r="H6">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6098,7 +6107,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>66</v>
@@ -6107,19 +6116,19 @@
         <v>37</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="2">
-        <v>86.5</v>
+        <v>83.8</v>
       </c>
       <c r="G7" s="2">
-        <v>13.5</v>
+        <v>16.2</v>
       </c>
       <c r="H7">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6169,7 +6178,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -6207,10 +6216,10 @@
         <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -6230,10 +6239,10 @@
         <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -6247,16 +6256,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920039</v>
+        <v>22330051920045</v>
       </c>
       <c r="B4" t="s">
         <v>72</v>
       </c>
       <c r="C4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -6270,22 +6279,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920039</v>
+        <v>22330051920045</v>
       </c>
       <c r="B5" t="s">
         <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -6299,10 +6308,10 @@
         <v>73</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -6311,6 +6320,29 @@
         <v>62</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920039</v>
+      </c>
+      <c r="B7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" t="s">
+        <v>82</v>
+      </c>
+      <c r="E7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
     </row>
